--- a/experiment_result/result.xlsx
+++ b/experiment_result/result.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Jupyter\aiops\experiment_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB1C498-4342-4EF1-8D17-B30AA552DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B875830E-0493-4ECE-B2AB-267FDF3A762C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="766" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="766" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="48label_cnn" sheetId="8" r:id="rId1"/>
     <sheet name="48label_lstm" sheetId="11" r:id="rId2"/>
     <sheet name="48label_bilstm" sheetId="12" r:id="rId3"/>
     <sheet name="48label_baseline" sheetId="5" r:id="rId4"/>
-    <sheet name="48label_ros" sheetId="6" r:id="rId5"/>
-    <sheet name="48label_word2vec" sheetId="7" r:id="rId6"/>
-    <sheet name="48label_word2vec+eda" sheetId="9" r:id="rId7"/>
-    <sheet name="48label_t5" sheetId="13" r:id="rId8"/>
-    <sheet name="8label_baseline" sheetId="15" r:id="rId9"/>
-    <sheet name="8label_ros" sheetId="16" r:id="rId10"/>
-    <sheet name="8label_word2vec" sheetId="17" r:id="rId11"/>
-    <sheet name="8label_eda" sheetId="18" r:id="rId12"/>
-    <sheet name="8label_t5" sheetId="19" r:id="rId13"/>
+    <sheet name="48label_ros_ir5" sheetId="20" r:id="rId5"/>
+    <sheet name="48label_ros" sheetId="6" r:id="rId6"/>
+    <sheet name="48label_word2vec" sheetId="7" r:id="rId7"/>
+    <sheet name="48label_word2vec+eda" sheetId="9" r:id="rId8"/>
+    <sheet name="48label_t5" sheetId="13" r:id="rId9"/>
+    <sheet name="8label_baseline" sheetId="15" r:id="rId10"/>
+    <sheet name="8label_ros" sheetId="16" r:id="rId11"/>
+    <sheet name="8label_word2vec" sheetId="17" r:id="rId12"/>
+    <sheet name="8label_eda" sheetId="18" r:id="rId13"/>
+    <sheet name="8label_t5" sheetId="19" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="354">
   <si>
     <t>val_accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1070,6 +1071,42 @@
   </si>
   <si>
     <t>8 hrs 34 mins 53 secs</t>
+  </si>
+  <si>
+    <t>Model_Config</t>
+  </si>
+  <si>
+    <t>1 hrs 3 mins 49 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 7 mins 5 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 30 mins 30 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 4 mins 10 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 1 mins 13 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 14 mins 8 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 23 mins 57 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 17 mins 53 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 15 mins 44 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 35 mins 46 secs</t>
+  </si>
+  <si>
+    <t>1 hrs 40 mins 44 secs</t>
   </si>
 </sst>
 </file>
@@ -2196,6 +2233,528 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBA8D9B-8D2C-414C-BA29-6A6C57C0308E}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="23">
+        <v>0.48563716252051842</v>
+      </c>
+      <c r="C2" s="23">
+        <v>0.86389283468334477</v>
+      </c>
+      <c r="D2" s="23">
+        <v>0.86506502964104148</v>
+      </c>
+      <c r="E2" s="23">
+        <v>0.86389283468334477</v>
+      </c>
+      <c r="F2" s="23">
+        <v>0.86388910167805899</v>
+      </c>
+      <c r="G2" s="23">
+        <v>0.86523224553062206</v>
+      </c>
+      <c r="H2" s="23">
+        <v>0.85829007260578416</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0.83232541542838379</v>
+      </c>
+      <c r="J2" s="23">
+        <v>0.1978527833270837</v>
+      </c>
+      <c r="K2" s="10">
+        <v>8113</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="23">
+        <v>0.44505702393408059</v>
+      </c>
+      <c r="C3" s="23">
+        <v>0.86530405967910795</v>
+      </c>
+      <c r="D3" s="23">
+        <v>0.86650496980919345</v>
+      </c>
+      <c r="E3" s="23">
+        <v>0.86530405967910795</v>
+      </c>
+      <c r="F3" s="23">
+        <v>0.86517024624575567</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0.86564074930484924</v>
+      </c>
+      <c r="H3" s="23">
+        <v>0.86222611105796898</v>
+      </c>
+      <c r="I3" s="23">
+        <v>0.83446257104405819</v>
+      </c>
+      <c r="J3" s="23">
+        <v>0.26683596902899798</v>
+      </c>
+      <c r="K3" s="10">
+        <v>7121</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="23">
+        <v>0.47696471087925102</v>
+      </c>
+      <c r="C4" s="23">
+        <v>0.86290964334490161</v>
+      </c>
+      <c r="D4" s="23">
+        <v>0.8646029949444699</v>
+      </c>
+      <c r="E4" s="23">
+        <v>0.86290964334490161</v>
+      </c>
+      <c r="F4" s="23">
+        <v>0.86286402104208793</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0.8622273415251408</v>
+      </c>
+      <c r="H4" s="23">
+        <v>0.85737182885398655</v>
+      </c>
+      <c r="I4" s="23">
+        <v>0.83146891809451551</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0.2282374234122112</v>
+      </c>
+      <c r="K4" s="10">
+        <v>8484</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="23">
+        <v>0.52649217649733127</v>
+      </c>
+      <c r="C5" s="23">
+        <v>0.86308068859208098</v>
+      </c>
+      <c r="D5" s="23">
+        <v>0.86432969858163966</v>
+      </c>
+      <c r="E5" s="23">
+        <v>0.86308068859208098</v>
+      </c>
+      <c r="F5" s="23">
+        <v>0.86282360511941092</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0.86096772831577773</v>
+      </c>
+      <c r="H5" s="23">
+        <v>0.8557255553488744</v>
+      </c>
+      <c r="I5" s="23">
+        <v>0.83174945662093314</v>
+      </c>
+      <c r="J5" s="23">
+        <v>0.16840544042059841</v>
+      </c>
+      <c r="K5" s="10">
+        <v>10221</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0.54067518540884918</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.86034399892031088</v>
+      </c>
+      <c r="D6" s="23">
+        <v>0.86184992712410557</v>
+      </c>
+      <c r="E6" s="23">
+        <v>0.86034399892031088</v>
+      </c>
+      <c r="F6" s="23">
+        <v>0.86012133638962462</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0.85969515199311264</v>
+      </c>
+      <c r="H6" s="23">
+        <v>0.86171575936603695</v>
+      </c>
+      <c r="I6" s="23">
+        <v>0.82888191926650856</v>
+      </c>
+      <c r="J6" s="23">
+        <v>0.17160472209496061</v>
+      </c>
+      <c r="K6" s="10">
+        <v>11227</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.42622931845900092</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.86402112661811947</v>
+      </c>
+      <c r="D7" s="23">
+        <v>0.86516738185608832</v>
+      </c>
+      <c r="E7" s="23">
+        <v>0.86402112661811947</v>
+      </c>
+      <c r="F7" s="23">
+        <v>0.86394399960600654</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0.86275075507822319</v>
+      </c>
+      <c r="H7" s="23">
+        <v>0.85886116135696489</v>
+      </c>
+      <c r="I7" s="23">
+        <v>0.83275729951537425</v>
+      </c>
+      <c r="J7" s="23">
+        <v>0.28903517864370593</v>
+      </c>
+      <c r="K7" s="10">
+        <v>8970</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0.49240507930310229</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.86122054467390874</v>
+      </c>
+      <c r="D8" s="23">
+        <v>0.86305760614139759</v>
+      </c>
+      <c r="E8" s="23">
+        <v>0.86122054467390874</v>
+      </c>
+      <c r="F8" s="23">
+        <v>0.8613564868344129</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0.85936507821178854</v>
+      </c>
+      <c r="H8" s="23">
+        <v>0.85836665793937228</v>
+      </c>
+      <c r="I8" s="23">
+        <v>0.82955039301493838</v>
+      </c>
+      <c r="J8" s="23">
+        <v>0.21217879638491521</v>
+      </c>
+      <c r="K8" s="10">
+        <v>11805</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="23">
+        <v>0.50240368200629215</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0.86089985140561287</v>
+      </c>
+      <c r="D9" s="23">
+        <v>0.86288456262408941</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.86089985140561287</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.86086893355422822</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.86008832338197083</v>
+      </c>
+      <c r="H9" s="23">
+        <v>0.85179494463529881</v>
+      </c>
+      <c r="I9" s="23">
+        <v>0.8288064728782869</v>
+      </c>
+      <c r="J9" s="23">
+        <v>0.23503039929181241</v>
+      </c>
+      <c r="K9" s="10">
+        <v>12728</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="23">
+        <v>0.7034693909124432</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0.74879781849772142</v>
+      </c>
+      <c r="D10" s="23">
+        <v>0.70886245341898235</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.74879781849772142</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.71685775313278766</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.70147387739599709</v>
+      </c>
+      <c r="H10" s="23">
+        <v>0.70800918000000856</v>
+      </c>
+      <c r="I10" s="23">
+        <v>0.66599390717368023</v>
+      </c>
+      <c r="J10" s="23">
+        <v>0.62481310801013545</v>
+      </c>
+      <c r="K10" s="10">
+        <v>7385</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0.87009745748594214</v>
+      </c>
+      <c r="C11" s="23">
+        <v>0.71065417527601027</v>
+      </c>
+      <c r="D11" s="23">
+        <v>0.66003135254924805</v>
+      </c>
+      <c r="E11" s="23">
+        <v>0.71065417527601027</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.67288022626212141</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.63696085801166558</v>
+      </c>
+      <c r="H11" s="23">
+        <v>0.64924618643610432</v>
+      </c>
+      <c r="I11" s="23">
+        <v>0.61865988702256414</v>
+      </c>
+      <c r="J11" s="23">
+        <v>0.73845397510924971</v>
+      </c>
+      <c r="K11" s="10">
+        <v>9013</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="23">
+        <v>1.5484072787836829</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0.40964011086240631</v>
+      </c>
+      <c r="D12" s="23">
+        <v>0.26951446285559499</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.40964011086240631</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.2945604516194768</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.22605950492680729</v>
+      </c>
+      <c r="H12" s="23">
+        <v>0.27945394779053129</v>
+      </c>
+      <c r="I12" s="23">
+        <v>0.20419850171722101</v>
+      </c>
+      <c r="J12" s="23">
+        <v>1.5108387243265451</v>
+      </c>
+      <c r="K12" s="10">
+        <v>6943</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="23">
+        <v>0.77067098743099183</v>
+      </c>
+      <c r="C13" s="23">
+        <v>0.73862121595988051</v>
+      </c>
+      <c r="D13" s="23">
+        <v>0.72440761786472785</v>
+      </c>
+      <c r="E13" s="23">
+        <v>0.73862121595988051</v>
+      </c>
+      <c r="F13" s="23">
+        <v>0.71978301146745438</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.69802912389502003</v>
+      </c>
+      <c r="H13" s="23">
+        <v>0.70851661727065762</v>
+      </c>
+      <c r="I13" s="23">
+        <v>0.66245592008531884</v>
+      </c>
+      <c r="J13" s="23">
+        <v>0.65174698696952338</v>
+      </c>
+      <c r="K13" s="10">
+        <v>10209</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="top10" dxfId="7" priority="2" rank="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C13">
+    <cfRule type="top10" dxfId="6" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A56776-98F4-4FC1-B099-5B0387F62249}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2718,7 +3277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EAB84C-2DEA-49B1-9D9B-5C60CA730376}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3242,7 +3801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75657C73-03F7-481B-9AEA-1F29C5109A0A}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3766,7 +4325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A336D564-D0D2-47EE-AEE8-619662B8B917}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -7838,6 +8397,487 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14754CE1-3768-4101-A92B-9F9CAC51DA21}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.62980316645271694</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.64070682392547296</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.62980316645271694</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.62361311380078999</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.41593739817863301</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.42634337722848198</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.51826169256072097</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1.87389085736216</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0.37151831865785201</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.61729316663875999</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.63984646711940696</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.61729316663875999</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.61527601990859404</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.414389135851153</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.42287389218862298</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.50614562928897899</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2.0001337023406398</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.36739248523474299</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.63438273241428</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.642481177423322</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.63438273241428</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.62911935005546904</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.42442816376158299</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.42890060850480499</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.52417931412833696</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.94727685364281</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.11359201579591099</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.62034694703354298</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.63620151880502396</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.62034694703354298</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.61658372444569798</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.41837086744815599</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.43265132331836798</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.50547826196024603</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1.75102962477178</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.47292269510521401</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.60174089784376095</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.63435417780303904</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.60174089784376095</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.606763867251224</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.40444601376427702</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.426839480911133</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.49670817134023598</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1.87216486927212</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.27344080102615598</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.607380444084761</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.63192039081600804</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.607380444084761</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.61081637482612094</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.41004189221011</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.42311258425797099</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.49812648270865501</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1.95738545478117</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.18053672372986701</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.58572200982307299</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.635876523170681</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.58572200982307299</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.59678247412673802</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.39615307150741202</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.43227526263564903</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.48038002381845102</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1.8771994777023699</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.40206070374138603</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.59532706368253596</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.63501176854417396</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.59532706368253596</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.60522941714013501</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.41479675790418302</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.44491259479010198</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.49110340506698502</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1.8425369048990801</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.29382510608742701</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.50931029190154598</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.308499881939788</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.50931029190154598</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.370888510062027</v>
+      </c>
+      <c r="F10" s="5">
+        <v>9.6396669905505106E-2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>9.7518678333713693E-2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.10975433559245799</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2.9655678317314198</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3.06265039038475</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.515246576807873</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.38643887894798001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.515246576807873</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.414290243912256</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.16669309322850501</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.18259633278757201</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.189660733067746</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2.96815299202756</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2.6627448974952799</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.46201221837733197</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.434786085507194</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.46201221837733197</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.42347969488385201</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.17260319172681299</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.205496217694909</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.237889105073331</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2.5422678924188302</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2.00019892659668</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.401892290375993</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.41732647658959499</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.401892290375993</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.38692220382807102</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.13564906395926199</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.17488359183798799</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.21790040482826301</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2.6675686193675499</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2.34339443858254</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FADA8-07B8-4272-9C6D-6AA1D1013DC4}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8362,7 +9402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42E03F8-CCBA-4CA7-B914-11C40186E5A7}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8926,7 +9966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDAE853-41FD-426B-83A6-86030E6D9E5C}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -9450,7 +10490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41F17F3-0237-45E9-80B4-1366CB6A8587}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -10006,526 +11046,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBA8D9B-8D2C-414C-BA29-6A6C57C0308E}">
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="23">
-        <v>0.48563716252051842</v>
-      </c>
-      <c r="C2" s="23">
-        <v>0.86389283468334477</v>
-      </c>
-      <c r="D2" s="23">
-        <v>0.86506502964104148</v>
-      </c>
-      <c r="E2" s="23">
-        <v>0.86389283468334477</v>
-      </c>
-      <c r="F2" s="23">
-        <v>0.86388910167805899</v>
-      </c>
-      <c r="G2" s="23">
-        <v>0.86523224553062206</v>
-      </c>
-      <c r="H2" s="23">
-        <v>0.85829007260578416</v>
-      </c>
-      <c r="I2" s="23">
-        <v>0.83232541542838379</v>
-      </c>
-      <c r="J2" s="23">
-        <v>0.1978527833270837</v>
-      </c>
-      <c r="K2" s="10">
-        <v>8113</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="23">
-        <v>0.44505702393408059</v>
-      </c>
-      <c r="C3" s="23">
-        <v>0.86530405967910795</v>
-      </c>
-      <c r="D3" s="23">
-        <v>0.86650496980919345</v>
-      </c>
-      <c r="E3" s="23">
-        <v>0.86530405967910795</v>
-      </c>
-      <c r="F3" s="23">
-        <v>0.86517024624575567</v>
-      </c>
-      <c r="G3" s="23">
-        <v>0.86564074930484924</v>
-      </c>
-      <c r="H3" s="23">
-        <v>0.86222611105796898</v>
-      </c>
-      <c r="I3" s="23">
-        <v>0.83446257104405819</v>
-      </c>
-      <c r="J3" s="23">
-        <v>0.26683596902899798</v>
-      </c>
-      <c r="K3" s="10">
-        <v>7121</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="23">
-        <v>0.47696471087925102</v>
-      </c>
-      <c r="C4" s="23">
-        <v>0.86290964334490161</v>
-      </c>
-      <c r="D4" s="23">
-        <v>0.8646029949444699</v>
-      </c>
-      <c r="E4" s="23">
-        <v>0.86290964334490161</v>
-      </c>
-      <c r="F4" s="23">
-        <v>0.86286402104208793</v>
-      </c>
-      <c r="G4" s="23">
-        <v>0.8622273415251408</v>
-      </c>
-      <c r="H4" s="23">
-        <v>0.85737182885398655</v>
-      </c>
-      <c r="I4" s="23">
-        <v>0.83146891809451551</v>
-      </c>
-      <c r="J4" s="23">
-        <v>0.2282374234122112</v>
-      </c>
-      <c r="K4" s="10">
-        <v>8484</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="23">
-        <v>0.52649217649733127</v>
-      </c>
-      <c r="C5" s="23">
-        <v>0.86308068859208098</v>
-      </c>
-      <c r="D5" s="23">
-        <v>0.86432969858163966</v>
-      </c>
-      <c r="E5" s="23">
-        <v>0.86308068859208098</v>
-      </c>
-      <c r="F5" s="23">
-        <v>0.86282360511941092</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0.86096772831577773</v>
-      </c>
-      <c r="H5" s="23">
-        <v>0.8557255553488744</v>
-      </c>
-      <c r="I5" s="23">
-        <v>0.83174945662093314</v>
-      </c>
-      <c r="J5" s="23">
-        <v>0.16840544042059841</v>
-      </c>
-      <c r="K5" s="10">
-        <v>10221</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="23">
-        <v>0.54067518540884918</v>
-      </c>
-      <c r="C6" s="23">
-        <v>0.86034399892031088</v>
-      </c>
-      <c r="D6" s="23">
-        <v>0.86184992712410557</v>
-      </c>
-      <c r="E6" s="23">
-        <v>0.86034399892031088</v>
-      </c>
-      <c r="F6" s="23">
-        <v>0.86012133638962462</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.85969515199311264</v>
-      </c>
-      <c r="H6" s="23">
-        <v>0.86171575936603695</v>
-      </c>
-      <c r="I6" s="23">
-        <v>0.82888191926650856</v>
-      </c>
-      <c r="J6" s="23">
-        <v>0.17160472209496061</v>
-      </c>
-      <c r="K6" s="10">
-        <v>11227</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="23">
-        <v>0.42622931845900092</v>
-      </c>
-      <c r="C7" s="23">
-        <v>0.86402112661811947</v>
-      </c>
-      <c r="D7" s="23">
-        <v>0.86516738185608832</v>
-      </c>
-      <c r="E7" s="23">
-        <v>0.86402112661811947</v>
-      </c>
-      <c r="F7" s="23">
-        <v>0.86394399960600654</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0.86275075507822319</v>
-      </c>
-      <c r="H7" s="23">
-        <v>0.85886116135696489</v>
-      </c>
-      <c r="I7" s="23">
-        <v>0.83275729951537425</v>
-      </c>
-      <c r="J7" s="23">
-        <v>0.28903517864370593</v>
-      </c>
-      <c r="K7" s="10">
-        <v>8970</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="23">
-        <v>0.49240507930310229</v>
-      </c>
-      <c r="C8" s="23">
-        <v>0.86122054467390874</v>
-      </c>
-      <c r="D8" s="23">
-        <v>0.86305760614139759</v>
-      </c>
-      <c r="E8" s="23">
-        <v>0.86122054467390874</v>
-      </c>
-      <c r="F8" s="23">
-        <v>0.8613564868344129</v>
-      </c>
-      <c r="G8" s="23">
-        <v>0.85936507821178854</v>
-      </c>
-      <c r="H8" s="23">
-        <v>0.85836665793937228</v>
-      </c>
-      <c r="I8" s="23">
-        <v>0.82955039301493838</v>
-      </c>
-      <c r="J8" s="23">
-        <v>0.21217879638491521</v>
-      </c>
-      <c r="K8" s="10">
-        <v>11805</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="23">
-        <v>0.50240368200629215</v>
-      </c>
-      <c r="C9" s="23">
-        <v>0.86089985140561287</v>
-      </c>
-      <c r="D9" s="23">
-        <v>0.86288456262408941</v>
-      </c>
-      <c r="E9" s="23">
-        <v>0.86089985140561287</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0.86086893355422822</v>
-      </c>
-      <c r="G9" s="23">
-        <v>0.86008832338197083</v>
-      </c>
-      <c r="H9" s="23">
-        <v>0.85179494463529881</v>
-      </c>
-      <c r="I9" s="23">
-        <v>0.8288064728782869</v>
-      </c>
-      <c r="J9" s="23">
-        <v>0.23503039929181241</v>
-      </c>
-      <c r="K9" s="10">
-        <v>12728</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="23">
-        <v>0.7034693909124432</v>
-      </c>
-      <c r="C10" s="23">
-        <v>0.74879781849772142</v>
-      </c>
-      <c r="D10" s="23">
-        <v>0.70886245341898235</v>
-      </c>
-      <c r="E10" s="23">
-        <v>0.74879781849772142</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0.71685775313278766</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.70147387739599709</v>
-      </c>
-      <c r="H10" s="23">
-        <v>0.70800918000000856</v>
-      </c>
-      <c r="I10" s="23">
-        <v>0.66599390717368023</v>
-      </c>
-      <c r="J10" s="23">
-        <v>0.62481310801013545</v>
-      </c>
-      <c r="K10" s="10">
-        <v>7385</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="23">
-        <v>0.87009745748594214</v>
-      </c>
-      <c r="C11" s="23">
-        <v>0.71065417527601027</v>
-      </c>
-      <c r="D11" s="23">
-        <v>0.66003135254924805</v>
-      </c>
-      <c r="E11" s="23">
-        <v>0.71065417527601027</v>
-      </c>
-      <c r="F11" s="23">
-        <v>0.67288022626212141</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0.63696085801166558</v>
-      </c>
-      <c r="H11" s="23">
-        <v>0.64924618643610432</v>
-      </c>
-      <c r="I11" s="23">
-        <v>0.61865988702256414</v>
-      </c>
-      <c r="J11" s="23">
-        <v>0.73845397510924971</v>
-      </c>
-      <c r="K11" s="10">
-        <v>9013</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="23">
-        <v>1.5484072787836829</v>
-      </c>
-      <c r="C12" s="23">
-        <v>0.40964011086240631</v>
-      </c>
-      <c r="D12" s="23">
-        <v>0.26951446285559499</v>
-      </c>
-      <c r="E12" s="23">
-        <v>0.40964011086240631</v>
-      </c>
-      <c r="F12" s="23">
-        <v>0.2945604516194768</v>
-      </c>
-      <c r="G12" s="23">
-        <v>0.22605950492680729</v>
-      </c>
-      <c r="H12" s="23">
-        <v>0.27945394779053129</v>
-      </c>
-      <c r="I12" s="23">
-        <v>0.20419850171722101</v>
-      </c>
-      <c r="J12" s="23">
-        <v>1.5108387243265451</v>
-      </c>
-      <c r="K12" s="10">
-        <v>6943</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="23">
-        <v>0.77067098743099183</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0.73862121595988051</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.72440761786472785</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.73862121595988051</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.71978301146745438</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.69802912389502003</v>
-      </c>
-      <c r="H13" s="23">
-        <v>0.70851661727065762</v>
-      </c>
-      <c r="I13" s="23">
-        <v>0.66245592008531884</v>
-      </c>
-      <c r="J13" s="23">
-        <v>0.65174698696952338</v>
-      </c>
-      <c r="K13" s="10">
-        <v>10209</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="7" priority="2" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
-    <cfRule type="top10" dxfId="6" priority="1" rank="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/experiment_result/result.xlsx
+++ b/experiment_result/result.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Jupyter\aiops\experiment_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B875830E-0493-4ECE-B2AB-267FDF3A762C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F259168-DDB5-4E94-BAD7-66328172EAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="766" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="766" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="48label_cnn" sheetId="8" r:id="rId1"/>
     <sheet name="48label_lstm" sheetId="11" r:id="rId2"/>
     <sheet name="48label_bilstm" sheetId="12" r:id="rId3"/>
     <sheet name="48label_baseline" sheetId="5" r:id="rId4"/>
-    <sheet name="48label_ros_ir5" sheetId="20" r:id="rId5"/>
-    <sheet name="48label_ros" sheetId="6" r:id="rId6"/>
-    <sheet name="48label_word2vec" sheetId="7" r:id="rId7"/>
-    <sheet name="48label_word2vec+eda" sheetId="9" r:id="rId8"/>
-    <sheet name="48label_t5" sheetId="13" r:id="rId9"/>
-    <sheet name="8label_baseline" sheetId="15" r:id="rId10"/>
-    <sheet name="8label_ros" sheetId="16" r:id="rId11"/>
-    <sheet name="8label_word2vec" sheetId="17" r:id="rId12"/>
-    <sheet name="8label_eda" sheetId="18" r:id="rId13"/>
-    <sheet name="8label_t5" sheetId="19" r:id="rId14"/>
+    <sheet name="48label_ros_ir2" sheetId="21" r:id="rId5"/>
+    <sheet name="48label_ros_ir5" sheetId="20" r:id="rId6"/>
+    <sheet name="48label_ros_ir10" sheetId="6" r:id="rId7"/>
+    <sheet name="48label_word2vec" sheetId="7" r:id="rId8"/>
+    <sheet name="48label_word2vec+eda" sheetId="9" r:id="rId9"/>
+    <sheet name="48label_t5" sheetId="13" r:id="rId10"/>
+    <sheet name="8label_baseline" sheetId="15" r:id="rId11"/>
+    <sheet name="8label_ros" sheetId="16" r:id="rId12"/>
+    <sheet name="8label_word2vec" sheetId="17" r:id="rId13"/>
+    <sheet name="8label_eda" sheetId="18" r:id="rId14"/>
+    <sheet name="8label_t5" sheetId="19" r:id="rId15"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="376">
   <si>
     <t>val_accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1107,6 +1108,72 @@
   </si>
   <si>
     <t>1 hrs 40 mins 44 secs</t>
+  </si>
+  <si>
+    <t>Val Loss</t>
+  </si>
+  <si>
+    <t>Val Accuracy</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>F1-Score</t>
+  </si>
+  <si>
+    <t>Macro F1</t>
+  </si>
+  <si>
+    <t>Balanced Acc</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>Train Loss</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>bert-base-uncased</t>
+  </si>
+  <si>
+    <t>bert-base-uncased + CNN</t>
+  </si>
+  <si>
+    <t>bert-base-uncased + LSTM</t>
+  </si>
+  <si>
+    <t>bert-base-uncased + BiLSTM</t>
+  </si>
+  <si>
+    <t>roberta-base</t>
+  </si>
+  <si>
+    <t>roberta-base + CNN</t>
+  </si>
+  <si>
+    <t>roberta-base + LSTM</t>
+  </si>
+  <si>
+    <t>roberta-base + BiLSTM</t>
+  </si>
+  <si>
+    <t>deberta-base</t>
+  </si>
+  <si>
+    <t>deberta-base + CNN</t>
+  </si>
+  <si>
+    <t>deberta-base + LSTM</t>
+  </si>
+  <si>
+    <t>deberta-base + BiLSTM</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1272,11 +1339,28 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1715,17 +1799,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E17CF8C-6CA7-44C1-B537-933EFCC02AFF}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="44.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1742,7 +1826,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>75</v>
       </c>
@@ -1762,7 +1846,7 @@
         <v>0.22989999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>76</v>
       </c>
@@ -1782,7 +1866,7 @@
         <v>0.19189999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>77</v>
       </c>
@@ -1802,7 +1886,7 @@
         <v>0.19919999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>78</v>
       </c>
@@ -1822,7 +1906,7 @@
         <v>0.1656</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
@@ -1842,7 +1926,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>80</v>
       </c>
@@ -1862,7 +1946,7 @@
         <v>0.3095</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>81</v>
       </c>
@@ -1882,7 +1966,7 @@
         <v>0.21290000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>82</v>
       </c>
@@ -1902,7 +1986,7 @@
         <v>0.1802</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>83</v>
       </c>
@@ -1922,7 +2006,7 @@
         <v>0.2437</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>84</v>
       </c>
@@ -1942,7 +2026,7 @@
         <v>0.38950000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>85</v>
       </c>
@@ -1962,7 +2046,7 @@
         <v>0.30259999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>86</v>
       </c>
@@ -1982,7 +2066,7 @@
         <v>0.3226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>87</v>
       </c>
@@ -2002,7 +2086,7 @@
         <v>1.2371000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -2022,7 +2106,7 @@
         <v>1.4414</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>89</v>
       </c>
@@ -2042,7 +2126,7 @@
         <v>0.59089999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>90</v>
       </c>
@@ -2062,7 +2146,7 @@
         <v>1.7483</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>91</v>
       </c>
@@ -2082,7 +2166,7 @@
         <v>0.75419999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>92</v>
       </c>
@@ -2102,7 +2186,7 @@
         <v>1.4823</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>93</v>
       </c>
@@ -2122,7 +2206,7 @@
         <v>0.33250000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>94</v>
       </c>
@@ -2142,7 +2226,7 @@
         <v>1.6876</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>95</v>
       </c>
@@ -2162,7 +2246,7 @@
         <v>0.3659</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>96</v>
       </c>
@@ -2182,7 +2266,7 @@
         <v>1.5825</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>97</v>
       </c>
@@ -2202,7 +2286,7 @@
         <v>1.7824</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>98</v>
       </c>
@@ -2225,7 +2309,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D2:D25">
-    <cfRule type="top10" dxfId="22" priority="1" rank="3"/>
+    <cfRule type="top10" dxfId="24" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2233,21 +2317,579 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41F17F3-0237-45E9-80B4-1366CB6A8587}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="18">
+        <v>2.2289966613599401</v>
+      </c>
+      <c r="C2" s="18">
+        <v>0.639415313203475</v>
+      </c>
+      <c r="D2" s="18">
+        <v>0.65068682015205304</v>
+      </c>
+      <c r="E2" s="18">
+        <v>0.639415313203475</v>
+      </c>
+      <c r="F2" s="18">
+        <v>0.63246585366907804</v>
+      </c>
+      <c r="G2" s="18">
+        <v>0.42430011001183299</v>
+      </c>
+      <c r="H2" s="18">
+        <v>0.41268145071012302</v>
+      </c>
+      <c r="I2" s="18">
+        <v>0.52519166776561099</v>
+      </c>
+      <c r="J2" s="18">
+        <v>0.115670414946195</v>
+      </c>
+      <c r="K2" s="4">
+        <v>11206</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="18">
+        <v>2.2038158333701299</v>
+      </c>
+      <c r="C3" s="18">
+        <v>0.63605770125206895</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0.64510310003867499</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0.63605770125206895</v>
+      </c>
+      <c r="F3" s="18">
+        <v>0.62624056297897601</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0.41274061304149701</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0.41722744778813498</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0.52165768424714698</v>
+      </c>
+      <c r="J3" s="18">
+        <v>0.37937119210269898</v>
+      </c>
+      <c r="K3" s="4">
+        <v>15239</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="18">
+        <v>1.8410535421858401</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.63468505237111805</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.64252379832189399</v>
+      </c>
+      <c r="E4" s="18">
+        <v>0.63468505237111805</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0.62799656466898301</v>
+      </c>
+      <c r="G4" s="18">
+        <v>0.40988431119723201</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0.43197689167018299</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0.52129152263788903</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0.58198165563455395</v>
+      </c>
+      <c r="K4" s="4">
+        <v>10105</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="18">
+        <v>2.2058255382427299</v>
+      </c>
+      <c r="C5" s="18">
+        <v>0.64993837323956705</v>
+      </c>
+      <c r="D5" s="18">
+        <v>0.64886394640481104</v>
+      </c>
+      <c r="E5" s="18">
+        <v>0.64993837323956705</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0.63979939601325797</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0.426306397695707</v>
+      </c>
+      <c r="H5" s="18">
+        <v>0.42492185735184002</v>
+      </c>
+      <c r="I5" s="18">
+        <v>0.53617965426203995</v>
+      </c>
+      <c r="J5" s="18">
+        <v>0.33220212649571501</v>
+      </c>
+      <c r="K5" s="4">
+        <v>16547</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="18">
+        <v>2.0051634905178299</v>
+      </c>
+      <c r="C6" s="18">
+        <v>0.62522767018287995</v>
+      </c>
+      <c r="D6" s="18">
+        <v>0.63519005768422998</v>
+      </c>
+      <c r="E6" s="18">
+        <v>0.62522767018287995</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0.61969057546065898</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.407377079440775</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.42234023395870701</v>
+      </c>
+      <c r="I6" s="18">
+        <v>0.50917153772274504</v>
+      </c>
+      <c r="J6" s="18">
+        <v>0.38880028879171102</v>
+      </c>
+      <c r="K6" s="4">
+        <v>21604</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="18">
+        <v>2.1132766196095298</v>
+      </c>
+      <c r="C7" s="18">
+        <v>0.63392669438708105</v>
+      </c>
+      <c r="D7" s="18">
+        <v>0.63868013050838801</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0.63392669438708105</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0.62587792038177803</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0.41639088686973402</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.422453815988311</v>
+      </c>
+      <c r="I7" s="18">
+        <v>0.51997285168371099</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0.30389512791704798</v>
+      </c>
+      <c r="K7" s="4">
+        <v>22627</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="18">
+        <v>2.24683170376754</v>
+      </c>
+      <c r="C8" s="18">
+        <v>0.59014460196089302</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0.54263316194877398</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0.59014460196089302</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0.54833042705742696</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0.31597091421435203</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.32295853702567701</v>
+      </c>
+      <c r="I8" s="18">
+        <v>0.398659970981113</v>
+      </c>
+      <c r="J8" s="18">
+        <v>1.1682616644029</v>
+      </c>
+      <c r="K8" s="4">
+        <v>23221</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="18">
+        <v>2.4295915400109598</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0.56665631802199001</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0.46465848740497701</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0.56665631802199001</v>
+      </c>
+      <c r="F9" s="18">
+        <v>0.48937571606485297</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0.22188853282277399</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.234643182639731</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0.33549019201014901</v>
+      </c>
+      <c r="J9" s="18">
+        <v>1.87515853551637</v>
+      </c>
+      <c r="K9" s="4">
+        <v>22242</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="18">
+        <v>2.3158342166644701</v>
+      </c>
+      <c r="C10" s="18">
+        <v>0.60478642257818405</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0.55555180994171904</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0.60478642257818405</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0.56273941066389899</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0.32746866097302302</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0.32765408222336001</v>
+      </c>
+      <c r="I10" s="18">
+        <v>0.41949665711399398</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0.98818393929395798</v>
+      </c>
+      <c r="K10" s="4">
+        <v>21300</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="18">
+        <v>2.5296481059818698</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0.59090726219047096</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0.55349975826229703</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.59090726219047096</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0.55485771768875503</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.31925129866330498</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.33020663650608501</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.40628760788485901</v>
+      </c>
+      <c r="J11" s="18">
+        <v>1.0116982194898101</v>
+      </c>
+      <c r="K11" s="4">
+        <v>22891</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B12" s="18">
+        <v>2.6606197288850399</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0.51098072593998201</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0.41254807289860801</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0.51098072593998201</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0.43818459664591197</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0.13111995483833899</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0.141765848596106</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0.26107131127136202</v>
+      </c>
+      <c r="J12" s="18">
+        <v>2.3707823125426999</v>
+      </c>
+      <c r="K12" s="4">
+        <v>12850</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" s="18">
+        <v>3.0558207325818998</v>
+      </c>
+      <c r="C13" s="18">
+        <v>0.46613644397313497</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0.27768801298037998</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0.46613644397313497</v>
+      </c>
+      <c r="F13" s="18">
+        <v>0.33978112073896499</v>
+      </c>
+      <c r="G13" s="18">
+        <v>2.5020099038473201E-2</v>
+      </c>
+      <c r="H13" s="18">
+        <v>4.1136765674076398E-2</v>
+      </c>
+      <c r="I13" s="18">
+        <v>0.14560984657555501</v>
+      </c>
+      <c r="J13" s="18">
+        <v>3.40151405680778</v>
+      </c>
+      <c r="K13" s="4">
+        <v>10847</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="17">
+        <f>AVERAGE(B2:B13)</f>
+        <v>2.3197064760981481</v>
+      </c>
+      <c r="C14" s="17">
+        <f t="shared" ref="C14:K14" si="0">AVERAGE(C2:C13)</f>
+        <v>0.59573854827507045</v>
+      </c>
+      <c r="D14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.55563559637890048</v>
+      </c>
+      <c r="E14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.59573854827507045</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.55877832183604514</v>
+      </c>
+      <c r="G14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31980990490058703</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.32749722917769458</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.42500670867968132</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.0764599611617867</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="0"/>
+        <v>17556.583333333332</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="top10" dxfId="10" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBA8D9B-8D2C-414C-BA29-6A6C57C0308E}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="13.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="10" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>281</v>
       </c>
@@ -2285,7 +2927,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>27</v>
       </c>
@@ -2323,7 +2965,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>29</v>
       </c>
@@ -2361,7 +3003,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>31</v>
       </c>
@@ -2399,7 +3041,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
@@ -2437,7 +3079,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
@@ -2475,7 +3117,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
@@ -2513,7 +3155,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>39</v>
       </c>
@@ -2551,7 +3193,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>41</v>
       </c>
@@ -2589,7 +3231,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>43</v>
       </c>
@@ -2627,7 +3269,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>45</v>
       </c>
@@ -2665,7 +3307,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
@@ -2703,7 +3345,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>49</v>
       </c>
@@ -2739,6 +3381,530 @@
       </c>
       <c r="L13" s="10" t="s">
         <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="top10" dxfId="9" priority="2" rank="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C13">
+    <cfRule type="top10" dxfId="8" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A56776-98F4-4FC1-B099-5B0387F62249}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.55516489361709331</v>
+      </c>
+      <c r="C2" s="25">
+        <v>0.86491915187722268</v>
+      </c>
+      <c r="D2" s="25">
+        <v>0.8653622709767077</v>
+      </c>
+      <c r="E2" s="25">
+        <v>0.86491915187722268</v>
+      </c>
+      <c r="F2" s="25">
+        <v>0.8648048153065846</v>
+      </c>
+      <c r="G2" s="25">
+        <v>0.86463345122205548</v>
+      </c>
+      <c r="H2" s="25">
+        <v>0.8610429297277109</v>
+      </c>
+      <c r="I2" s="25">
+        <v>0.8337076504180253</v>
+      </c>
+      <c r="J2" s="25">
+        <v>8.6929469595755843E-2</v>
+      </c>
+      <c r="K2" s="16">
+        <v>12558</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="25">
+        <v>0.51808854958155925</v>
+      </c>
+      <c r="C3" s="25">
+        <v>0.86305919765887551</v>
+      </c>
+      <c r="D3" s="25">
+        <v>0.86515692683366241</v>
+      </c>
+      <c r="E3" s="25">
+        <v>0.86305919765887551</v>
+      </c>
+      <c r="F3" s="25">
+        <v>0.86314879525261701</v>
+      </c>
+      <c r="G3" s="25">
+        <v>0.86332367852949832</v>
+      </c>
+      <c r="H3" s="25">
+        <v>0.85800873191357385</v>
+      </c>
+      <c r="I3" s="25">
+        <v>0.83173484814188969</v>
+      </c>
+      <c r="J3" s="25">
+        <v>0.1445908544838426</v>
+      </c>
+      <c r="K3" s="16">
+        <v>10517</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="25">
+        <v>0.50041339309316957</v>
+      </c>
+      <c r="C4" s="25">
+        <v>0.86293083944343896</v>
+      </c>
+      <c r="D4" s="25">
+        <v>0.8644371624690923</v>
+      </c>
+      <c r="E4" s="25">
+        <v>0.86293083944343896</v>
+      </c>
+      <c r="F4" s="25">
+        <v>0.86305509819098791</v>
+      </c>
+      <c r="G4" s="25">
+        <v>0.86098723173108771</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.85601434769044304</v>
+      </c>
+      <c r="I4" s="25">
+        <v>0.83128742909126563</v>
+      </c>
+      <c r="J4" s="25">
+        <v>0.16105756005936181</v>
+      </c>
+      <c r="K4" s="16">
+        <v>10766</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="25">
+        <v>0.58896866082886434</v>
+      </c>
+      <c r="C5" s="25">
+        <v>0.86181907733433349</v>
+      </c>
+      <c r="D5" s="25">
+        <v>0.86305206648394717</v>
+      </c>
+      <c r="E5" s="25">
+        <v>0.86181907733433349</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0.86173690953295368</v>
+      </c>
+      <c r="G5" s="25">
+        <v>0.86143229898612428</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0.85570855259509426</v>
+      </c>
+      <c r="I5" s="25">
+        <v>0.82976964646305884</v>
+      </c>
+      <c r="J5" s="25">
+        <v>8.067136929604217E-2</v>
+      </c>
+      <c r="K5" s="16">
+        <v>14895</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="25">
+        <v>0.49303287728092621</v>
+      </c>
+      <c r="C6" s="25">
+        <v>0.86117770679652195</v>
+      </c>
+      <c r="D6" s="25">
+        <v>0.86313417331612075</v>
+      </c>
+      <c r="E6" s="25">
+        <v>0.86117770679652195</v>
+      </c>
+      <c r="F6" s="25">
+        <v>0.86115873086295047</v>
+      </c>
+      <c r="G6" s="25">
+        <v>0.8601062014535964</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0.86576127031575356</v>
+      </c>
+      <c r="I6" s="25">
+        <v>0.82962230287942018</v>
+      </c>
+      <c r="J6" s="25">
+        <v>0.18423207023815599</v>
+      </c>
+      <c r="K6" s="16">
+        <v>11319</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0.8053445222214437</v>
+      </c>
+      <c r="C7" s="25">
+        <v>0.74764348134833614</v>
+      </c>
+      <c r="D7" s="25">
+        <v>0.70784339250966688</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0.74764348134833614</v>
+      </c>
+      <c r="F7" s="25">
+        <v>0.71585526449223713</v>
+      </c>
+      <c r="G7" s="25">
+        <v>0.69983739524594835</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.71456144757959383</v>
+      </c>
+      <c r="I7" s="25">
+        <v>0.66496150649122154</v>
+      </c>
+      <c r="J7" s="25">
+        <v>0.53231488747355948</v>
+      </c>
+      <c r="K7" s="16">
+        <v>13089</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0.53372889981402138</v>
+      </c>
+      <c r="C8" s="25">
+        <v>0.86184048598809682</v>
+      </c>
+      <c r="D8" s="25">
+        <v>0.86293816463009132</v>
+      </c>
+      <c r="E8" s="25">
+        <v>0.86184048598809682</v>
+      </c>
+      <c r="F8" s="25">
+        <v>0.86198392051266681</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.86149427777888943</v>
+      </c>
+      <c r="H8" s="25">
+        <v>0.86121770888936333</v>
+      </c>
+      <c r="I8" s="25">
+        <v>0.83004772649063641</v>
+      </c>
+      <c r="J8" s="25">
+        <v>0.18109184077877191</v>
+      </c>
+      <c r="K8" s="16">
+        <v>15767</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0.55173622988769389</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0.86124180248202786</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0.86248813398095547</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0.86124180248202786</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0.86131008632364259</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0.86033466304095452</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0.86166858288718517</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0.82946280864929123</v>
+      </c>
+      <c r="J9" s="25">
+        <v>0.14044694532575619</v>
+      </c>
+      <c r="K9" s="16">
+        <v>18122</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="25">
+        <v>1.091658301543142</v>
+      </c>
+      <c r="C10" s="25">
+        <v>0.63169298523186845</v>
+      </c>
+      <c r="D10" s="25">
+        <v>0.55036525333361486</v>
+      </c>
+      <c r="E10" s="25">
+        <v>0.63169298523186845</v>
+      </c>
+      <c r="F10" s="25">
+        <v>0.56802404894853142</v>
+      </c>
+      <c r="G10" s="25">
+        <v>0.53917661866356192</v>
+      </c>
+      <c r="H10" s="25">
+        <v>0.56334800075506453</v>
+      </c>
+      <c r="I10" s="25">
+        <v>0.49710294669905258</v>
+      </c>
+      <c r="J10" s="25">
+        <v>0.8799108203213738</v>
+      </c>
+      <c r="K10" s="16">
+        <v>9962</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="25">
+        <v>1.101687490355868</v>
+      </c>
+      <c r="C11" s="25">
+        <v>0.62688527400254179</v>
+      </c>
+      <c r="D11" s="25">
+        <v>0.54598463112423212</v>
+      </c>
+      <c r="E11" s="25">
+        <v>0.62688527400254179</v>
+      </c>
+      <c r="F11" s="25">
+        <v>0.56310711951336923</v>
+      </c>
+      <c r="G11" s="25">
+        <v>0.53544121616603924</v>
+      </c>
+      <c r="H11" s="25">
+        <v>0.56684830953439003</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0.49176800199843612</v>
+      </c>
+      <c r="J11" s="25">
+        <v>0.96683916621913146</v>
+      </c>
+      <c r="K11" s="16">
+        <v>9656</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0.53226040822414</v>
+      </c>
+      <c r="C12" s="25">
+        <v>0.84332501739581678</v>
+      </c>
+      <c r="D12" s="25">
+        <v>0.84628023262389296</v>
+      </c>
+      <c r="E12" s="25">
+        <v>0.84332501739581678</v>
+      </c>
+      <c r="F12" s="25">
+        <v>0.84345848208731344</v>
+      </c>
+      <c r="G12" s="25">
+        <v>0.84102378991124271</v>
+      </c>
+      <c r="H12" s="25">
+        <v>0.85398363337497352</v>
+      </c>
+      <c r="I12" s="25">
+        <v>0.80817171935832399</v>
+      </c>
+      <c r="J12" s="25">
+        <v>0.33344239572838058</v>
+      </c>
+      <c r="K12" s="16">
+        <v>13088</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0.61885767887863852</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0.80704099927468387</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0.81117325406859153</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.80704099927468387</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.80545954131484354</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.80277391350519056</v>
+      </c>
+      <c r="H13" s="25">
+        <v>0.81678868131645932</v>
+      </c>
+      <c r="I13" s="25">
+        <v>0.76375804121483504</v>
+      </c>
+      <c r="J13" s="25">
+        <v>0.5686564225806926</v>
+      </c>
+      <c r="K13" s="16">
+        <v>13417</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -2750,519 +3916,518 @@
     <cfRule type="top10" dxfId="6" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A56776-98F4-4FC1-B099-5B0387F62249}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EAB84C-2DEA-49B1-9D9B-5C60CA730376}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="39.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="25">
-        <v>0.55516489361709331</v>
-      </c>
-      <c r="C2" s="25">
-        <v>0.86491915187722268</v>
-      </c>
-      <c r="D2" s="25">
-        <v>0.8653622709767077</v>
-      </c>
-      <c r="E2" s="25">
-        <v>0.86491915187722268</v>
-      </c>
-      <c r="F2" s="25">
-        <v>0.8648048153065846</v>
-      </c>
-      <c r="G2" s="25">
-        <v>0.86463345122205548</v>
-      </c>
-      <c r="H2" s="25">
-        <v>0.8610429297277109</v>
-      </c>
-      <c r="I2" s="25">
-        <v>0.8337076504180253</v>
-      </c>
-      <c r="J2" s="25">
-        <v>8.6929469595755843E-2</v>
-      </c>
-      <c r="K2" s="16">
-        <v>12558</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="25">
-        <v>0.51808854958155925</v>
-      </c>
-      <c r="C3" s="25">
-        <v>0.86305919765887551</v>
-      </c>
-      <c r="D3" s="25">
-        <v>0.86515692683366241</v>
-      </c>
-      <c r="E3" s="25">
-        <v>0.86305919765887551</v>
-      </c>
-      <c r="F3" s="25">
-        <v>0.86314879525261701</v>
-      </c>
-      <c r="G3" s="25">
-        <v>0.86332367852949832</v>
-      </c>
-      <c r="H3" s="25">
-        <v>0.85800873191357385</v>
-      </c>
-      <c r="I3" s="25">
-        <v>0.83173484814188969</v>
-      </c>
-      <c r="J3" s="25">
-        <v>0.1445908544838426</v>
-      </c>
-      <c r="K3" s="16">
-        <v>10517</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="25">
-        <v>0.50041339309316957</v>
-      </c>
-      <c r="C4" s="25">
-        <v>0.86293083944343896</v>
-      </c>
-      <c r="D4" s="25">
-        <v>0.8644371624690923</v>
-      </c>
-      <c r="E4" s="25">
-        <v>0.86293083944343896</v>
-      </c>
-      <c r="F4" s="25">
-        <v>0.86305509819098791</v>
-      </c>
-      <c r="G4" s="25">
-        <v>0.86098723173108771</v>
-      </c>
-      <c r="H4" s="25">
-        <v>0.85601434769044304</v>
-      </c>
-      <c r="I4" s="25">
-        <v>0.83128742909126563</v>
-      </c>
-      <c r="J4" s="25">
-        <v>0.16105756005936181</v>
-      </c>
-      <c r="K4" s="16">
-        <v>10766</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="25">
-        <v>0.58896866082886434</v>
-      </c>
-      <c r="C5" s="25">
-        <v>0.86181907733433349</v>
-      </c>
-      <c r="D5" s="25">
-        <v>0.86305206648394717</v>
-      </c>
-      <c r="E5" s="25">
-        <v>0.86181907733433349</v>
-      </c>
-      <c r="F5" s="25">
-        <v>0.86173690953295368</v>
-      </c>
-      <c r="G5" s="25">
-        <v>0.86143229898612428</v>
-      </c>
-      <c r="H5" s="25">
-        <v>0.85570855259509426</v>
-      </c>
-      <c r="I5" s="25">
-        <v>0.82976964646305884</v>
-      </c>
-      <c r="J5" s="25">
-        <v>8.067136929604217E-2</v>
-      </c>
-      <c r="K5" s="16">
-        <v>14895</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="25">
-        <v>0.49303287728092621</v>
-      </c>
-      <c r="C6" s="25">
-        <v>0.86117770679652195</v>
-      </c>
-      <c r="D6" s="25">
-        <v>0.86313417331612075</v>
-      </c>
-      <c r="E6" s="25">
-        <v>0.86117770679652195</v>
-      </c>
-      <c r="F6" s="25">
-        <v>0.86115873086295047</v>
-      </c>
-      <c r="G6" s="25">
-        <v>0.8601062014535964</v>
-      </c>
-      <c r="H6" s="25">
-        <v>0.86576127031575356</v>
-      </c>
-      <c r="I6" s="25">
-        <v>0.82962230287942018</v>
-      </c>
-      <c r="J6" s="25">
-        <v>0.18423207023815599</v>
-      </c>
-      <c r="K6" s="16">
-        <v>11319</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="25">
-        <v>0.8053445222214437</v>
-      </c>
-      <c r="C7" s="25">
-        <v>0.74764348134833614</v>
-      </c>
-      <c r="D7" s="25">
-        <v>0.70784339250966688</v>
-      </c>
-      <c r="E7" s="25">
-        <v>0.74764348134833614</v>
-      </c>
-      <c r="F7" s="25">
-        <v>0.71585526449223713</v>
-      </c>
-      <c r="G7" s="25">
-        <v>0.69983739524594835</v>
-      </c>
-      <c r="H7" s="25">
-        <v>0.71456144757959383</v>
-      </c>
-      <c r="I7" s="25">
-        <v>0.66496150649122154</v>
-      </c>
-      <c r="J7" s="25">
-        <v>0.53231488747355948</v>
-      </c>
-      <c r="K7" s="16">
-        <v>13089</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="25">
-        <v>0.53372889981402138</v>
-      </c>
-      <c r="C8" s="25">
-        <v>0.86184048598809682</v>
-      </c>
-      <c r="D8" s="25">
-        <v>0.86293816463009132</v>
-      </c>
-      <c r="E8" s="25">
-        <v>0.86184048598809682</v>
-      </c>
-      <c r="F8" s="25">
-        <v>0.86198392051266681</v>
-      </c>
-      <c r="G8" s="25">
-        <v>0.86149427777888943</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.86121770888936333</v>
-      </c>
-      <c r="I8" s="25">
-        <v>0.83004772649063641</v>
-      </c>
-      <c r="J8" s="25">
-        <v>0.18109184077877191</v>
-      </c>
-      <c r="K8" s="16">
-        <v>15767</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="25">
-        <v>0.55173622988769389</v>
-      </c>
-      <c r="C9" s="25">
-        <v>0.86124180248202786</v>
-      </c>
-      <c r="D9" s="25">
-        <v>0.86248813398095547</v>
-      </c>
-      <c r="E9" s="25">
-        <v>0.86124180248202786</v>
-      </c>
-      <c r="F9" s="25">
-        <v>0.86131008632364259</v>
-      </c>
-      <c r="G9" s="25">
-        <v>0.86033466304095452</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.86166858288718517</v>
-      </c>
-      <c r="I9" s="25">
-        <v>0.82946280864929123</v>
-      </c>
-      <c r="J9" s="25">
-        <v>0.14044694532575619</v>
-      </c>
-      <c r="K9" s="16">
-        <v>18122</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="25">
-        <v>1.091658301543142</v>
-      </c>
-      <c r="C10" s="25">
-        <v>0.63169298523186845</v>
-      </c>
-      <c r="D10" s="25">
-        <v>0.55036525333361486</v>
-      </c>
-      <c r="E10" s="25">
-        <v>0.63169298523186845</v>
-      </c>
-      <c r="F10" s="25">
-        <v>0.56802404894853142</v>
-      </c>
-      <c r="G10" s="25">
-        <v>0.53917661866356192</v>
-      </c>
-      <c r="H10" s="25">
-        <v>0.56334800075506453</v>
-      </c>
-      <c r="I10" s="25">
-        <v>0.49710294669905258</v>
-      </c>
-      <c r="J10" s="25">
-        <v>0.8799108203213738</v>
-      </c>
-      <c r="K10" s="16">
-        <v>9962</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="25">
-        <v>1.101687490355868</v>
-      </c>
-      <c r="C11" s="25">
-        <v>0.62688527400254179</v>
-      </c>
-      <c r="D11" s="25">
-        <v>0.54598463112423212</v>
-      </c>
-      <c r="E11" s="25">
-        <v>0.62688527400254179</v>
-      </c>
-      <c r="F11" s="25">
-        <v>0.56310711951336923</v>
-      </c>
-      <c r="G11" s="25">
-        <v>0.53544121616603924</v>
-      </c>
-      <c r="H11" s="25">
-        <v>0.56684830953439003</v>
-      </c>
-      <c r="I11" s="25">
-        <v>0.49176800199843612</v>
-      </c>
-      <c r="J11" s="25">
-        <v>0.96683916621913146</v>
-      </c>
-      <c r="K11" s="16">
-        <v>9656</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="25">
-        <v>0.53226040822414</v>
-      </c>
-      <c r="C12" s="25">
-        <v>0.84332501739581678</v>
-      </c>
-      <c r="D12" s="25">
-        <v>0.84628023262389296</v>
-      </c>
-      <c r="E12" s="25">
-        <v>0.84332501739581678</v>
-      </c>
-      <c r="F12" s="25">
-        <v>0.84345848208731344</v>
-      </c>
-      <c r="G12" s="25">
-        <v>0.84102378991124271</v>
-      </c>
-      <c r="H12" s="25">
-        <v>0.85398363337497352</v>
-      </c>
-      <c r="I12" s="25">
-        <v>0.80817171935832399</v>
-      </c>
-      <c r="J12" s="25">
-        <v>0.33344239572838058</v>
-      </c>
-      <c r="K12" s="16">
-        <v>13088</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="25">
-        <v>0.61885767887863852</v>
-      </c>
-      <c r="C13" s="25">
-        <v>0.80704099927468387</v>
-      </c>
-      <c r="D13" s="25">
-        <v>0.81117325406859153</v>
-      </c>
-      <c r="E13" s="25">
-        <v>0.80704099927468387</v>
-      </c>
-      <c r="F13" s="25">
-        <v>0.80545954131484354</v>
-      </c>
-      <c r="G13" s="25">
-        <v>0.80277391350519056</v>
-      </c>
-      <c r="H13" s="25">
-        <v>0.81678868131645932</v>
-      </c>
-      <c r="I13" s="25">
-        <v>0.76375804121483504</v>
-      </c>
-      <c r="J13" s="25">
-        <v>0.5686564225806926</v>
-      </c>
-      <c r="K13" s="16">
-        <v>13417</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>305</v>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19">
+        <v>0.48466835060745928</v>
+      </c>
+      <c r="C2" s="19">
+        <v>0.8626315708276866</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0.86377067509686933</v>
+      </c>
+      <c r="E2" s="19">
+        <v>0.8626315708276866</v>
+      </c>
+      <c r="F2" s="19">
+        <v>0.86260352711526767</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0.86025191039122828</v>
+      </c>
+      <c r="H2" s="19">
+        <v>0.86052938149257585</v>
+      </c>
+      <c r="I2" s="19">
+        <v>0.83120633278964939</v>
+      </c>
+      <c r="J2" s="19">
+        <v>0.1549383954692399</v>
+      </c>
+      <c r="K2" s="13">
+        <v>9517</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19">
+        <v>0.49712542135885351</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0.86209687558674086</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0.86388631734035659</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0.86209687558674086</v>
+      </c>
+      <c r="F3" s="19">
+        <v>0.86218694568088561</v>
+      </c>
+      <c r="G3" s="19">
+        <v>0.861926080430365</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0.85679158440959213</v>
+      </c>
+      <c r="I3" s="19">
+        <v>0.83031064775967833</v>
+      </c>
+      <c r="J3" s="19">
+        <v>0.14773696763792321</v>
+      </c>
+      <c r="K3" s="13">
+        <v>10283</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="19">
+        <v>0.47804491623828149</v>
+      </c>
+      <c r="C4" s="19">
+        <v>0.85726515475906007</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.85942716647475259</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.85726515475906007</v>
+      </c>
+      <c r="F4" s="19">
+        <v>0.85745118389431041</v>
+      </c>
+      <c r="G4" s="19">
+        <v>0.85689350963194288</v>
+      </c>
+      <c r="H4" s="19">
+        <v>0.85681102468641546</v>
+      </c>
+      <c r="I4" s="19">
+        <v>0.82493045517156582</v>
+      </c>
+      <c r="J4" s="19">
+        <v>0.2376524728827204</v>
+      </c>
+      <c r="K4" s="13">
+        <v>9286</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="19">
+        <v>0.49940771113977672</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0.86286673004469261</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.8637267826022702</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.86286673004469261</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0.86293164344632189</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0.86027860068892392</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0.8651410001733717</v>
+      </c>
+      <c r="I5" s="19">
+        <v>0.83153387517785615</v>
+      </c>
+      <c r="J5" s="19">
+        <v>0.1540935632762141</v>
+      </c>
+      <c r="K5" s="13">
+        <v>11451</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="19">
+        <v>0.5303444640939402</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.86085706381010729</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.86235656964030005</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.86085706381010729</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.86091240749947651</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.85811412481276361</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.85953877382993615</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.82900863241038303</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.14711852356320371</v>
+      </c>
+      <c r="K6" s="13">
+        <v>13982</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="19">
+        <v>0.77751139327008123</v>
+      </c>
+      <c r="C7" s="19">
+        <v>0.74518463792531464</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0.70543138553400753</v>
+      </c>
+      <c r="E7" s="19">
+        <v>0.74518463792531464</v>
+      </c>
+      <c r="F7" s="19">
+        <v>0.71335046780053368</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0.69786392247634221</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0.71660420592969931</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.66227901017254509</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0.59582832686659071</v>
+      </c>
+      <c r="K7" s="13">
+        <v>11578</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0.49682935176648069</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0.85694428321863936</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0.85876513484075956</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0.85694428321863936</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0.85712373109526641</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0.85529876880650568</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0.85587056965797037</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.82422490477605703</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0.2989124885622515</v>
+      </c>
+      <c r="K8" s="13">
+        <v>11867</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="19">
+        <v>0.48346935095520233</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0.85514839954485766</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0.85729439181062028</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0.85514839954485766</v>
+      </c>
+      <c r="F9" s="19">
+        <v>0.85513716390155126</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.85379898168352786</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.85894390070888238</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.82236027506825859</v>
+      </c>
+      <c r="J9" s="19">
+        <v>0.27655136505696332</v>
+      </c>
+      <c r="K9" s="13">
+        <v>11579</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="19">
+        <v>0.78037383042116715</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0.74300362932334196</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0.70359935451477584</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0.74300362932334196</v>
+      </c>
+      <c r="F10" s="19">
+        <v>0.71114654241184971</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0.69533061042733757</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0.71434043764190291</v>
+      </c>
+      <c r="I10" s="19">
+        <v>0.65973883461085125</v>
+      </c>
+      <c r="J10" s="19">
+        <v>0.5939513962610643</v>
+      </c>
+      <c r="K10" s="13">
+        <v>11062</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.0676171872328619</v>
+      </c>
+      <c r="C11" s="19">
+        <v>0.6281349227436035</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0.54681165269435184</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0.6281349227436035</v>
+      </c>
+      <c r="F11" s="19">
+        <v>0.56446693733630393</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0.53504468048551546</v>
+      </c>
+      <c r="H11" s="19">
+        <v>0.56664418137501404</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0.49325206748009121</v>
+      </c>
+      <c r="J11" s="19">
+        <v>0.9878046287674136</v>
+      </c>
+      <c r="K11" s="13">
+        <v>9694</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="19">
+        <v>0.8384747832723789</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0.72733187995840765</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0.68788125865614991</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0.72733187995840765</v>
+      </c>
+      <c r="F12" s="19">
+        <v>0.69563632168468204</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0.67807706284735492</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0.70166887109687626</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.64054084307468329</v>
+      </c>
+      <c r="J12" s="19">
+        <v>0.74084043145571066</v>
+      </c>
+      <c r="K12" s="13">
+        <v>12413</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="19">
+        <v>1.132773497573331</v>
+      </c>
+      <c r="C13" s="19">
+        <v>0.60572798393539595</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0.52887310612017546</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0.60572798393539595</v>
+      </c>
+      <c r="F13" s="19">
+        <v>0.54278711775601207</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.51659002569898438</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0.55443939990118274</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.49338459675682261</v>
+      </c>
+      <c r="J13" s="19">
+        <v>1.1924987504038851</v>
+      </c>
+      <c r="K13" s="13">
+        <v>12251</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3274,27 +4439,28 @@
     <cfRule type="top10" dxfId="4" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EAB84C-2DEA-49B1-9D9B-5C60CA730376}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75657C73-03F7-481B-9AEA-1F29C5109A0A}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.875" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>281</v>
       </c>
@@ -3332,460 +4498,460 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="B2" s="19">
-        <v>0.48466835060745928</v>
+        <v>0.45411646615697909</v>
       </c>
       <c r="C2" s="19">
-        <v>0.8626315708276866</v>
+        <v>0.86023691679731384</v>
       </c>
       <c r="D2" s="19">
-        <v>0.86377067509686933</v>
+        <v>0.86187604971550691</v>
       </c>
       <c r="E2" s="19">
-        <v>0.8626315708276866</v>
+        <v>0.86023691679731384</v>
       </c>
       <c r="F2" s="19">
-        <v>0.86260352711526767</v>
+        <v>0.86015812851229201</v>
       </c>
       <c r="G2" s="19">
-        <v>0.86025191039122828</v>
+        <v>0.8576542799378164</v>
       </c>
       <c r="H2" s="19">
-        <v>0.86052938149257585</v>
+        <v>0.86055159264476444</v>
       </c>
       <c r="I2" s="19">
-        <v>0.83120633278964939</v>
+        <v>0.82844611255785949</v>
       </c>
       <c r="J2" s="19">
-        <v>0.1549383954692399</v>
+        <v>0.2039991148189885</v>
       </c>
       <c r="K2" s="13">
-        <v>9517</v>
+        <v>9227</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="B3" s="19">
-        <v>0.49712542135885351</v>
+        <v>0.5322021139340285</v>
       </c>
       <c r="C3" s="19">
-        <v>0.86209687558674086</v>
+        <v>0.86224671787876284</v>
       </c>
       <c r="D3" s="19">
-        <v>0.86388631734035659</v>
+        <v>0.86292847767940706</v>
       </c>
       <c r="E3" s="19">
-        <v>0.86209687558674086</v>
+        <v>0.86224671787876284</v>
       </c>
       <c r="F3" s="19">
-        <v>0.86218694568088561</v>
+        <v>0.86209893659309267</v>
       </c>
       <c r="G3" s="19">
-        <v>0.861926080430365</v>
+        <v>0.86092836673987383</v>
       </c>
       <c r="H3" s="19">
-        <v>0.85679158440959213</v>
+        <v>0.85792011780812416</v>
       </c>
       <c r="I3" s="19">
-        <v>0.83031064775967833</v>
+        <v>0.83053946864156258</v>
       </c>
       <c r="J3" s="19">
-        <v>0.14773696763792321</v>
+        <v>0.12323423403495951</v>
       </c>
       <c r="K3" s="13">
-        <v>10283</v>
+        <v>11440</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B4" s="19">
-        <v>0.47804491623828149</v>
+        <v>0.47712236738429431</v>
       </c>
       <c r="C4" s="19">
-        <v>0.85726515475906007</v>
+        <v>0.85968120144441562</v>
       </c>
       <c r="D4" s="19">
-        <v>0.85942716647475259</v>
+        <v>0.86170729590419515</v>
       </c>
       <c r="E4" s="19">
-        <v>0.85726515475906007</v>
+        <v>0.85968120144441562</v>
       </c>
       <c r="F4" s="19">
-        <v>0.85745118389431041</v>
+        <v>0.85980541914022834</v>
       </c>
       <c r="G4" s="19">
-        <v>0.85689350963194288</v>
+        <v>0.85762293952540247</v>
       </c>
       <c r="H4" s="19">
-        <v>0.85681102468641546</v>
+        <v>0.8575236539022667</v>
       </c>
       <c r="I4" s="19">
-        <v>0.82493045517156582</v>
+        <v>0.82762679114350457</v>
       </c>
       <c r="J4" s="19">
-        <v>0.2376524728827204</v>
+        <v>0.18306836959744391</v>
       </c>
       <c r="K4" s="13">
-        <v>9286</v>
+        <v>10525</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="B5" s="19">
-        <v>0.49940771113977672</v>
+        <v>0.4546703318692743</v>
       </c>
       <c r="C5" s="19">
-        <v>0.86286673004469261</v>
+        <v>0.86303781871713314</v>
       </c>
       <c r="D5" s="19">
-        <v>0.8637267826022702</v>
+        <v>0.86420318271023544</v>
       </c>
       <c r="E5" s="19">
-        <v>0.86286673004469261</v>
+        <v>0.86303781871713314</v>
       </c>
       <c r="F5" s="19">
-        <v>0.86293164344632189</v>
+        <v>0.86313011322251343</v>
       </c>
       <c r="G5" s="19">
-        <v>0.86027860068892392</v>
+        <v>0.85995759778468783</v>
       </c>
       <c r="H5" s="19">
-        <v>0.8651410001733717</v>
+        <v>0.86546351593067405</v>
       </c>
       <c r="I5" s="19">
-        <v>0.83153387517785615</v>
+        <v>0.83185230924275899</v>
       </c>
       <c r="J5" s="19">
-        <v>0.1540935632762141</v>
+        <v>0.20547014861867149</v>
       </c>
       <c r="K5" s="13">
-        <v>11451</v>
+        <v>9896</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="B6" s="19">
-        <v>0.5303444640939402</v>
+        <v>0.81971876584717795</v>
       </c>
       <c r="C6" s="19">
-        <v>0.86085706381010729</v>
+        <v>0.74640335873825392</v>
       </c>
       <c r="D6" s="19">
-        <v>0.86235656964030005</v>
+        <v>0.70648050174217847</v>
       </c>
       <c r="E6" s="19">
-        <v>0.86085706381010729</v>
+        <v>0.74640335873825392</v>
       </c>
       <c r="F6" s="19">
-        <v>0.86091240749947651</v>
+        <v>0.71457339423773925</v>
       </c>
       <c r="G6" s="19">
-        <v>0.85811412481276361</v>
+        <v>0.69784984830319252</v>
       </c>
       <c r="H6" s="19">
-        <v>0.85953877382993615</v>
+        <v>0.71252654896596079</v>
       </c>
       <c r="I6" s="19">
-        <v>0.82900863241038303</v>
+        <v>0.66346022997670018</v>
       </c>
       <c r="J6" s="19">
-        <v>0.14711852356320371</v>
+        <v>0.52084991083213228</v>
       </c>
       <c r="K6" s="13">
-        <v>13982</v>
+        <v>12552</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B7" s="19">
-        <v>0.77751139327008123</v>
+        <v>0.49753215412044127</v>
       </c>
       <c r="C7" s="19">
-        <v>0.74518463792531464</v>
+        <v>0.85921070473827876</v>
       </c>
       <c r="D7" s="19">
-        <v>0.70543138553400753</v>
+        <v>0.861340588565365</v>
       </c>
       <c r="E7" s="19">
-        <v>0.74518463792531464</v>
+        <v>0.85921070473827876</v>
       </c>
       <c r="F7" s="19">
-        <v>0.71335046780053368</v>
+        <v>0.85944005721834649</v>
       </c>
       <c r="G7" s="19">
-        <v>0.69786392247634221</v>
+        <v>0.85646036836568895</v>
       </c>
       <c r="H7" s="19">
-        <v>0.71660420592969931</v>
+        <v>0.85968632031819059</v>
       </c>
       <c r="I7" s="19">
-        <v>0.66227901017254509</v>
+        <v>0.82708970549800165</v>
       </c>
       <c r="J7" s="19">
-        <v>0.59582832686659071</v>
+        <v>0.16316091432711069</v>
       </c>
       <c r="K7" s="13">
-        <v>11578</v>
+        <v>15434</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="B8" s="19">
-        <v>0.49682935176648069</v>
+        <v>0.45993984887249068</v>
       </c>
       <c r="C8" s="19">
-        <v>0.85694428321863936</v>
+        <v>0.85461398085425944</v>
       </c>
       <c r="D8" s="19">
-        <v>0.85876513484075956</v>
+        <v>0.85716629668656485</v>
       </c>
       <c r="E8" s="19">
-        <v>0.85694428321863936</v>
+        <v>0.85461398085425944</v>
       </c>
       <c r="F8" s="19">
-        <v>0.85712373109526641</v>
+        <v>0.85472334670674965</v>
       </c>
       <c r="G8" s="19">
-        <v>0.85529876880650568</v>
+        <v>0.8528457408870832</v>
       </c>
       <c r="H8" s="19">
-        <v>0.85587056965797037</v>
+        <v>0.8631356086019123</v>
       </c>
       <c r="I8" s="19">
-        <v>0.82422490477605703</v>
+        <v>0.82223907358266324</v>
       </c>
       <c r="J8" s="19">
-        <v>0.2989124885622515</v>
+        <v>0.31322677678222288</v>
       </c>
       <c r="K8" s="13">
-        <v>11867</v>
+        <v>10325</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B9" s="19">
-        <v>0.48346935095520233</v>
+        <v>0.52755873215567861</v>
       </c>
       <c r="C9" s="19">
-        <v>0.85514839954485766</v>
+        <v>0.85942452386772339</v>
       </c>
       <c r="D9" s="19">
-        <v>0.85729439181062028</v>
+        <v>0.86063007729950569</v>
       </c>
       <c r="E9" s="19">
-        <v>0.85514839954485766</v>
+        <v>0.85942452386772339</v>
       </c>
       <c r="F9" s="19">
-        <v>0.85513716390155126</v>
+        <v>0.85948532757616491</v>
       </c>
       <c r="G9" s="19">
-        <v>0.85379898168352786</v>
+        <v>0.85626428171917879</v>
       </c>
       <c r="H9" s="19">
-        <v>0.85894390070888238</v>
+        <v>0.85169936924774559</v>
       </c>
       <c r="I9" s="19">
-        <v>0.82236027506825859</v>
+        <v>0.82683386757671384</v>
       </c>
       <c r="J9" s="19">
-        <v>0.27655136505696332</v>
+        <v>0.19449805906349099</v>
       </c>
       <c r="K9" s="13">
-        <v>11579</v>
+        <v>17051</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="B10" s="19">
-        <v>0.78037383042116715</v>
+        <v>0.76538623122386951</v>
       </c>
       <c r="C10" s="19">
-        <v>0.74300362932334196</v>
+        <v>0.73712390381213222</v>
       </c>
       <c r="D10" s="19">
-        <v>0.70359935451477584</v>
+        <v>0.70046038020394907</v>
       </c>
       <c r="E10" s="19">
-        <v>0.74300362932334196</v>
+        <v>0.73712390381213222</v>
       </c>
       <c r="F10" s="19">
-        <v>0.71114654241184971</v>
+        <v>0.70601696423420979</v>
       </c>
       <c r="G10" s="19">
-        <v>0.69533061042733757</v>
+        <v>0.68621254000645648</v>
       </c>
       <c r="H10" s="19">
-        <v>0.71434043764190291</v>
+        <v>0.70929594677452745</v>
       </c>
       <c r="I10" s="19">
-        <v>0.65973883461085125</v>
+        <v>0.65261958310931611</v>
       </c>
       <c r="J10" s="19">
-        <v>0.5939513962610643</v>
+        <v>0.73695971087390943</v>
       </c>
       <c r="K10" s="13">
-        <v>11062</v>
+        <v>8754</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="B11" s="19">
-        <v>1.0676171872328619</v>
+        <v>1.0984893140472221</v>
       </c>
       <c r="C11" s="19">
-        <v>0.6281349227436035</v>
+        <v>0.62271358286174061</v>
       </c>
       <c r="D11" s="19">
-        <v>0.54681165269435184</v>
+        <v>0.54353378471931546</v>
       </c>
       <c r="E11" s="19">
-        <v>0.6281349227436035</v>
+        <v>0.62271358286174061</v>
       </c>
       <c r="F11" s="19">
-        <v>0.56446693733630393</v>
+        <v>0.55899802520945119</v>
       </c>
       <c r="G11" s="19">
-        <v>0.53504468048551546</v>
+        <v>0.5277364267170338</v>
       </c>
       <c r="H11" s="19">
-        <v>0.56664418137501404</v>
+        <v>0.56383222089535001</v>
       </c>
       <c r="I11" s="19">
-        <v>0.49325206748009121</v>
+        <v>0.48745664106132541</v>
       </c>
       <c r="J11" s="19">
-        <v>0.9878046287674136</v>
+        <v>0.79862720470768211</v>
       </c>
       <c r="K11" s="13">
-        <v>9694</v>
+        <v>10410</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="B12" s="19">
-        <v>0.8384747832723789</v>
+        <v>0.77808228016504621</v>
       </c>
       <c r="C12" s="19">
-        <v>0.72733187995840765</v>
+        <v>0.72068339019185623</v>
       </c>
       <c r="D12" s="19">
-        <v>0.68788125865614991</v>
+        <v>0.7204365356861292</v>
       </c>
       <c r="E12" s="19">
-        <v>0.72733187995840765</v>
+        <v>0.72068339019185623</v>
       </c>
       <c r="F12" s="19">
-        <v>0.69563632168468204</v>
+        <v>0.69384304153120013</v>
       </c>
       <c r="G12" s="19">
-        <v>0.67807706284735492</v>
+        <v>0.69590831978014089</v>
       </c>
       <c r="H12" s="19">
-        <v>0.70166887109687626</v>
+        <v>0.72307480183161998</v>
       </c>
       <c r="I12" s="19">
-        <v>0.64054084307468329</v>
+        <v>0.66768890924934388</v>
       </c>
       <c r="J12" s="19">
-        <v>0.74084043145571066</v>
+        <v>0.70849032962439984</v>
       </c>
       <c r="K12" s="13">
-        <v>12413</v>
+        <v>11329</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="B13" s="19">
-        <v>1.132773497573331</v>
+        <v>1.089717375384246</v>
       </c>
       <c r="C13" s="19">
-        <v>0.60572798393539595</v>
+        <v>0.62158054694573561</v>
       </c>
       <c r="D13" s="19">
-        <v>0.52887310612017546</v>
+        <v>0.54106929752713606</v>
       </c>
       <c r="E13" s="19">
-        <v>0.60572798393539595</v>
+        <v>0.62158054694573561</v>
       </c>
       <c r="F13" s="19">
-        <v>0.54278711775601207</v>
+        <v>0.55793918724963487</v>
       </c>
       <c r="G13" s="19">
-        <v>0.51659002569898438</v>
+        <v>0.5276049102237923</v>
       </c>
       <c r="H13" s="19">
-        <v>0.55443939990118274</v>
+        <v>0.55984943048524038</v>
       </c>
       <c r="I13" s="19">
-        <v>0.49338459675682261</v>
+        <v>0.4851435141629154</v>
       </c>
       <c r="J13" s="19">
-        <v>1.1924987504038851</v>
+        <v>1.014923522745117</v>
       </c>
       <c r="K13" s="13">
-        <v>12251</v>
+        <v>12015</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3801,548 +4967,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75657C73-03F7-481B-9AEA-1F29C5109A0A}">
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="43.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0.45411646615697909</v>
-      </c>
-      <c r="C2" s="19">
-        <v>0.86023691679731384</v>
-      </c>
-      <c r="D2" s="19">
-        <v>0.86187604971550691</v>
-      </c>
-      <c r="E2" s="19">
-        <v>0.86023691679731384</v>
-      </c>
-      <c r="F2" s="19">
-        <v>0.86015812851229201</v>
-      </c>
-      <c r="G2" s="19">
-        <v>0.8576542799378164</v>
-      </c>
-      <c r="H2" s="19">
-        <v>0.86055159264476444</v>
-      </c>
-      <c r="I2" s="19">
-        <v>0.82844611255785949</v>
-      </c>
-      <c r="J2" s="19">
-        <v>0.2039991148189885</v>
-      </c>
-      <c r="K2" s="13">
-        <v>9227</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="19">
-        <v>0.5322021139340285</v>
-      </c>
-      <c r="C3" s="19">
-        <v>0.86224671787876284</v>
-      </c>
-      <c r="D3" s="19">
-        <v>0.86292847767940706</v>
-      </c>
-      <c r="E3" s="19">
-        <v>0.86224671787876284</v>
-      </c>
-      <c r="F3" s="19">
-        <v>0.86209893659309267</v>
-      </c>
-      <c r="G3" s="19">
-        <v>0.86092836673987383</v>
-      </c>
-      <c r="H3" s="19">
-        <v>0.85792011780812416</v>
-      </c>
-      <c r="I3" s="19">
-        <v>0.83053946864156258</v>
-      </c>
-      <c r="J3" s="19">
-        <v>0.12323423403495951</v>
-      </c>
-      <c r="K3" s="13">
-        <v>11440</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="19">
-        <v>0.47712236738429431</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0.85968120144441562</v>
-      </c>
-      <c r="D4" s="19">
-        <v>0.86170729590419515</v>
-      </c>
-      <c r="E4" s="19">
-        <v>0.85968120144441562</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0.85980541914022834</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.85762293952540247</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.8575236539022667</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0.82762679114350457</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.18306836959744391</v>
-      </c>
-      <c r="K4" s="13">
-        <v>10525</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="19">
-        <v>0.4546703318692743</v>
-      </c>
-      <c r="C5" s="19">
-        <v>0.86303781871713314</v>
-      </c>
-      <c r="D5" s="19">
-        <v>0.86420318271023544</v>
-      </c>
-      <c r="E5" s="19">
-        <v>0.86303781871713314</v>
-      </c>
-      <c r="F5" s="19">
-        <v>0.86313011322251343</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0.85995759778468783</v>
-      </c>
-      <c r="H5" s="19">
-        <v>0.86546351593067405</v>
-      </c>
-      <c r="I5" s="19">
-        <v>0.83185230924275899</v>
-      </c>
-      <c r="J5" s="19">
-        <v>0.20547014861867149</v>
-      </c>
-      <c r="K5" s="13">
-        <v>9896</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="19">
-        <v>0.81971876584717795</v>
-      </c>
-      <c r="C6" s="19">
-        <v>0.74640335873825392</v>
-      </c>
-      <c r="D6" s="19">
-        <v>0.70648050174217847</v>
-      </c>
-      <c r="E6" s="19">
-        <v>0.74640335873825392</v>
-      </c>
-      <c r="F6" s="19">
-        <v>0.71457339423773925</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.69784984830319252</v>
-      </c>
-      <c r="H6" s="19">
-        <v>0.71252654896596079</v>
-      </c>
-      <c r="I6" s="19">
-        <v>0.66346022997670018</v>
-      </c>
-      <c r="J6" s="19">
-        <v>0.52084991083213228</v>
-      </c>
-      <c r="K6" s="13">
-        <v>12552</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="19">
-        <v>0.49753215412044127</v>
-      </c>
-      <c r="C7" s="19">
-        <v>0.85921070473827876</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0.861340588565365</v>
-      </c>
-      <c r="E7" s="19">
-        <v>0.85921070473827876</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0.85944005721834649</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.85646036836568895</v>
-      </c>
-      <c r="H7" s="19">
-        <v>0.85968632031819059</v>
-      </c>
-      <c r="I7" s="19">
-        <v>0.82708970549800165</v>
-      </c>
-      <c r="J7" s="19">
-        <v>0.16316091432711069</v>
-      </c>
-      <c r="K7" s="13">
-        <v>15434</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="19">
-        <v>0.45993984887249068</v>
-      </c>
-      <c r="C8" s="19">
-        <v>0.85461398085425944</v>
-      </c>
-      <c r="D8" s="19">
-        <v>0.85716629668656485</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0.85461398085425944</v>
-      </c>
-      <c r="F8" s="19">
-        <v>0.85472334670674965</v>
-      </c>
-      <c r="G8" s="19">
-        <v>0.8528457408870832</v>
-      </c>
-      <c r="H8" s="19">
-        <v>0.8631356086019123</v>
-      </c>
-      <c r="I8" s="19">
-        <v>0.82223907358266324</v>
-      </c>
-      <c r="J8" s="19">
-        <v>0.31322677678222288</v>
-      </c>
-      <c r="K8" s="13">
-        <v>10325</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="19">
-        <v>0.52755873215567861</v>
-      </c>
-      <c r="C9" s="19">
-        <v>0.85942452386772339</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0.86063007729950569</v>
-      </c>
-      <c r="E9" s="19">
-        <v>0.85942452386772339</v>
-      </c>
-      <c r="F9" s="19">
-        <v>0.85948532757616491</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0.85626428171917879</v>
-      </c>
-      <c r="H9" s="19">
-        <v>0.85169936924774559</v>
-      </c>
-      <c r="I9" s="19">
-        <v>0.82683386757671384</v>
-      </c>
-      <c r="J9" s="19">
-        <v>0.19449805906349099</v>
-      </c>
-      <c r="K9" s="13">
-        <v>17051</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="19">
-        <v>0.76538623122386951</v>
-      </c>
-      <c r="C10" s="19">
-        <v>0.73712390381213222</v>
-      </c>
-      <c r="D10" s="19">
-        <v>0.70046038020394907</v>
-      </c>
-      <c r="E10" s="19">
-        <v>0.73712390381213222</v>
-      </c>
-      <c r="F10" s="19">
-        <v>0.70601696423420979</v>
-      </c>
-      <c r="G10" s="19">
-        <v>0.68621254000645648</v>
-      </c>
-      <c r="H10" s="19">
-        <v>0.70929594677452745</v>
-      </c>
-      <c r="I10" s="19">
-        <v>0.65261958310931611</v>
-      </c>
-      <c r="J10" s="19">
-        <v>0.73695971087390943</v>
-      </c>
-      <c r="K10" s="13">
-        <v>8754</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="19">
-        <v>1.0984893140472221</v>
-      </c>
-      <c r="C11" s="19">
-        <v>0.62271358286174061</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0.54353378471931546</v>
-      </c>
-      <c r="E11" s="19">
-        <v>0.62271358286174061</v>
-      </c>
-      <c r="F11" s="19">
-        <v>0.55899802520945119</v>
-      </c>
-      <c r="G11" s="19">
-        <v>0.5277364267170338</v>
-      </c>
-      <c r="H11" s="19">
-        <v>0.56383222089535001</v>
-      </c>
-      <c r="I11" s="19">
-        <v>0.48745664106132541</v>
-      </c>
-      <c r="J11" s="19">
-        <v>0.79862720470768211</v>
-      </c>
-      <c r="K11" s="13">
-        <v>10410</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="19">
-        <v>0.77808228016504621</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.72068339019185623</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.7204365356861292</v>
-      </c>
-      <c r="E12" s="19">
-        <v>0.72068339019185623</v>
-      </c>
-      <c r="F12" s="19">
-        <v>0.69384304153120013</v>
-      </c>
-      <c r="G12" s="19">
-        <v>0.69590831978014089</v>
-      </c>
-      <c r="H12" s="19">
-        <v>0.72307480183161998</v>
-      </c>
-      <c r="I12" s="19">
-        <v>0.66768890924934388</v>
-      </c>
-      <c r="J12" s="19">
-        <v>0.70849032962439984</v>
-      </c>
-      <c r="K12" s="13">
-        <v>11329</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="19">
-        <v>1.089717375384246</v>
-      </c>
-      <c r="C13" s="19">
-        <v>0.62158054694573561</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0.54106929752713606</v>
-      </c>
-      <c r="E13" s="19">
-        <v>0.62158054694573561</v>
-      </c>
-      <c r="F13" s="19">
-        <v>0.55793918724963487</v>
-      </c>
-      <c r="G13" s="19">
-        <v>0.5276049102237923</v>
-      </c>
-      <c r="H13" s="19">
-        <v>0.55984943048524038</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0.4851435141629154</v>
-      </c>
-      <c r="J13" s="19">
-        <v>1.014923522745117</v>
-      </c>
-      <c r="K13" s="13">
-        <v>12015</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>329</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="1" priority="2" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
-    <cfRule type="top10" dxfId="0" priority="1" rank="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A336D564-D0D2-47EE-AEE8-619662B8B917}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>281</v>
       </c>
@@ -4380,7 +5022,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>257</v>
       </c>
@@ -4418,7 +5060,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>259</v>
       </c>
@@ -4456,7 +5098,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>261</v>
       </c>
@@ -4494,7 +5136,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>263</v>
       </c>
@@ -4532,7 +5174,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>265</v>
       </c>
@@ -4570,7 +5212,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>267</v>
       </c>
@@ -4608,7 +5250,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>269</v>
       </c>
@@ -4646,7 +5288,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>271</v>
       </c>
@@ -4684,7 +5326,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>273</v>
       </c>
@@ -4722,7 +5364,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>275</v>
       </c>
@@ -4760,7 +5402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>277</v>
       </c>
@@ -4798,7 +5440,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>279</v>
       </c>
@@ -4845,22 +5487,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0C40CF-9E11-462F-8582-3FB0EBEA4697}">
   <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.25" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>135</v>
       </c>
@@ -4901,7 +5543,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>137</v>
       </c>
@@ -4942,7 +5584,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>137</v>
       </c>
@@ -4983,7 +5625,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>137</v>
       </c>
@@ -5024,7 +5666,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>137</v>
       </c>
@@ -5065,7 +5707,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>137</v>
       </c>
@@ -5106,7 +5748,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>137</v>
       </c>
@@ -5147,7 +5789,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>137</v>
       </c>
@@ -5188,7 +5830,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>137</v>
       </c>
@@ -5229,7 +5871,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>137</v>
       </c>
@@ -5270,7 +5912,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>137</v>
       </c>
@@ -5311,7 +5953,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>137</v>
       </c>
@@ -5352,7 +5994,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>137</v>
       </c>
@@ -5393,7 +6035,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>162</v>
       </c>
@@ -5434,7 +6076,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>162</v>
       </c>
@@ -5475,7 +6117,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>162</v>
       </c>
@@ -5516,7 +6158,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>162</v>
       </c>
@@ -5557,7 +6199,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>162</v>
       </c>
@@ -5598,7 +6240,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>162</v>
       </c>
@@ -5639,7 +6281,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>162</v>
       </c>
@@ -5680,7 +6322,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>162</v>
       </c>
@@ -5721,7 +6363,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>162</v>
       </c>
@@ -5762,7 +6404,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>162</v>
       </c>
@@ -5803,7 +6445,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>162</v>
       </c>
@@ -5844,7 +6486,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>162</v>
       </c>
@@ -5885,7 +6527,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>175</v>
       </c>
@@ -5926,7 +6568,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>175</v>
       </c>
@@ -5967,7 +6609,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>175</v>
       </c>
@@ -6008,7 +6650,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>175</v>
       </c>
@@ -6049,7 +6691,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>175</v>
       </c>
@@ -6090,7 +6732,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>175</v>
       </c>
@@ -6131,7 +6773,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>175</v>
       </c>
@@ -6172,7 +6814,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>175</v>
       </c>
@@ -6213,7 +6855,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>175</v>
       </c>
@@ -6254,7 +6896,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>175</v>
       </c>
@@ -6295,7 +6937,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>175</v>
       </c>
@@ -6336,7 +6978,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>175</v>
       </c>
@@ -6380,7 +7022,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2:H37">
-    <cfRule type="top10" dxfId="21" priority="1" rank="5"/>
+    <cfRule type="top10" dxfId="23" priority="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6389,19 +7031,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8372B9FC-9562-4E8A-824D-682F839CA250}">
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="6"/>
+    <col min="11" max="11" width="12.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>186</v>
       </c>
@@ -6439,7 +7081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>187</v>
       </c>
@@ -6477,7 +7119,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>189</v>
       </c>
@@ -6515,7 +7157,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>191</v>
       </c>
@@ -6553,7 +7195,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>193</v>
       </c>
@@ -6591,7 +7233,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>195</v>
       </c>
@@ -6629,7 +7271,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>197</v>
       </c>
@@ -6667,7 +7309,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>199</v>
       </c>
@@ -6705,7 +7347,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>201</v>
       </c>
@@ -6743,7 +7385,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>203</v>
       </c>
@@ -6781,7 +7423,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>205</v>
       </c>
@@ -6819,7 +7461,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>207</v>
       </c>
@@ -6857,7 +7499,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>209</v>
       </c>
@@ -6895,7 +7537,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>211</v>
       </c>
@@ -6933,7 +7575,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>213</v>
       </c>
@@ -6971,7 +7613,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>215</v>
       </c>
@@ -7009,7 +7651,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>216</v>
       </c>
@@ -7047,7 +7689,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>218</v>
       </c>
@@ -7085,7 +7727,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>220</v>
       </c>
@@ -7123,7 +7765,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>222</v>
       </c>
@@ -7161,7 +7803,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>224</v>
       </c>
@@ -7199,7 +7841,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>226</v>
       </c>
@@ -7237,7 +7879,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>228</v>
       </c>
@@ -7275,7 +7917,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>230</v>
       </c>
@@ -7313,7 +7955,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>232</v>
       </c>
@@ -7351,7 +7993,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>233</v>
       </c>
@@ -7389,7 +8031,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>235</v>
       </c>
@@ -7427,7 +8069,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>237</v>
       </c>
@@ -7465,7 +8107,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>239</v>
       </c>
@@ -7503,7 +8145,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>241</v>
       </c>
@@ -7541,7 +8183,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>243</v>
       </c>
@@ -7579,7 +8221,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>245</v>
       </c>
@@ -7617,7 +8259,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>247</v>
       </c>
@@ -7655,7 +8297,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>249</v>
       </c>
@@ -7693,7 +8335,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>251</v>
       </c>
@@ -7731,7 +8373,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>253</v>
       </c>
@@ -7769,7 +8411,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>255</v>
       </c>
@@ -7810,7 +8452,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G37">
-    <cfRule type="top10" dxfId="20" priority="1" rank="5"/>
+    <cfRule type="top10" dxfId="22" priority="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7820,21 +8462,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B2AF50-4881-4BD8-ABC8-BC15E9EA58C5}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>17</v>
@@ -7870,7 +8512,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -7908,7 +8550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
@@ -7946,7 +8588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
@@ -7984,7 +8626,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -8022,7 +8664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
@@ -8060,7 +8702,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -8098,7 +8740,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>39</v>
       </c>
@@ -8136,7 +8778,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>41</v>
       </c>
@@ -8174,7 +8816,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -8212,7 +8854,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -8250,7 +8892,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -8288,7 +8930,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
@@ -8326,7 +8968,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="21">
         <f>AVERAGE(B2:B13)</f>
         <v>1.8824113866507322</v>
@@ -8371,24 +9013,1509 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:B13">
-    <cfRule type="top10" dxfId="19" priority="7" bottom="1" rank="3"/>
+    <cfRule type="top10" dxfId="21" priority="7" bottom="1" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C13">
-    <cfRule type="top10" dxfId="18" priority="6" rank="3"/>
+    <cfRule type="top10" dxfId="20" priority="6" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D13">
-    <cfRule type="top10" dxfId="17" priority="5" rank="3"/>
+    <cfRule type="top10" dxfId="19" priority="5" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E13">
-    <cfRule type="top10" dxfId="16" priority="4" rank="3"/>
+    <cfRule type="top10" dxfId="18" priority="4" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F13">
-    <cfRule type="top10" dxfId="15" priority="3" rank="3"/>
+    <cfRule type="top10" dxfId="17" priority="3" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G13">
+    <cfRule type="top10" dxfId="16" priority="2" rank="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H13">
+    <cfRule type="top10" dxfId="15" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A136C9-2F22-4F16-862A-CF928C3720C8}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="9" style="6"/>
+    <col min="7" max="7" width="9.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1.9775</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.62860000000000005</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.62860000000000005</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.62329999999999997</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.41820000000000002</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.4224</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.51959999999999995</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0.29870000000000002</v>
+      </c>
+      <c r="K2" s="26">
+        <v>8.4328703703703697E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2.2959000000000001</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.6069</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.6069</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.61209999999999998</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.41810000000000003</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.43919999999999998</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.50419999999999998</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.30509999999999998</v>
+      </c>
+      <c r="K3" s="26">
+        <v>0.10151620370370371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2.0651999999999999</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.60340000000000005</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.6321</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.60340000000000005</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.60719999999999996</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.40789999999999998</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.42680000000000001</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.49740000000000001</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.1108</v>
+      </c>
+      <c r="K4" s="26">
+        <v>9.7129629629629635E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1.9448000000000001</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.61750000000000005</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.63180000000000003</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.61750000000000005</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.61570000000000003</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.41689999999999999</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.42449999999999999</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.23219999999999999</v>
+      </c>
+      <c r="K5" s="26">
+        <v>9.331018518518519E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" s="6">
+        <v>2.7362000000000002</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.45390000000000003</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.45390000000000003</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.42130000000000001</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.25059999999999999</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.2828</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.3024</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1.7225999999999999</v>
+      </c>
+      <c r="K6" s="26">
+        <v>9.8356481481481475E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2.2376</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.62739999999999996</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.60850000000000004</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.41880000000000001</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.4345</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.4945</v>
+      </c>
+      <c r="J7" s="6">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="K7" s="26">
+        <v>0.16627314814814814</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B8" s="6">
+        <v>2.0960999999999999</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.57520000000000004</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.61990000000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.57520000000000004</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.58450000000000002</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.40250000000000002</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.4299</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.47270000000000001</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.1983</v>
+      </c>
+      <c r="K8" s="26">
+        <v>0.11321759259259259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2.6191</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.54039999999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.5544</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.54039999999999999</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.52170000000000005</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.3246</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.3513</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.37169999999999997</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.88939999999999997</v>
+      </c>
+      <c r="K9" s="26">
+        <v>0.12791666666666668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B10" s="6">
+        <v>2.8694000000000002</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.4667</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.41880000000000001</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.4667</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.4279</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.2341</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.2336</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1.5788</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0.11106481481481481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B11" s="6">
+        <v>2.9483999999999999</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.54679999999999995</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.46689999999999998</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.54679999999999995</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.48159999999999997</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.2475</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.29139999999999999</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1.802</v>
+      </c>
+      <c r="K11" s="26">
+        <v>0.11586805555555556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2.9226000000000001</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.28449999999999998</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.28449999999999998</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.31309999999999999</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.14230000000000001</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.18809999999999999</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.19120000000000001</v>
+      </c>
+      <c r="J12" s="6">
+        <v>2.2141999999999999</v>
+      </c>
+      <c r="K12" s="26">
+        <v>0.12591435185185185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13" s="6">
+        <v>3.1347</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.53129999999999999</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.3805</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.53129999999999999</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.42559999999999998</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.16259999999999999</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.1605</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.19869999999999999</v>
+      </c>
+      <c r="J13" s="6">
+        <v>2.2692999999999999</v>
+      </c>
+      <c r="K13" s="26">
+        <v>0.15810185185185185</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="top10" dxfId="0" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14754CE1-3768-4101-A92B-9F9CAC51DA21}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.62980316645271694</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.64070682392547296</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.62980316645271694</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.62361311380078999</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.41593739817863301</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.42634337722848198</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.51826169256072097</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1.87389085736216</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0.37151831865785201</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.61729316663875999</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.63984646711940696</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.61729316663875999</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.61527601990859404</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.414389135851153</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.42287389218862298</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.50614562928897899</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2.0001337023406398</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.36739248523474299</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.63438273241428</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.642481177423322</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.63438273241428</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.62911935005546904</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.42442816376158299</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.42890060850480499</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.52417931412833696</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.94727685364281</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.11359201579591099</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.62034694703354298</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.63620151880502396</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.62034694703354298</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.61658372444569798</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.41837086744815599</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.43265132331836798</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.50547826196024603</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1.75102962477178</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.47292269510521401</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.60174089784376095</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.63435417780303904</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.60174089784376095</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.606763867251224</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.40444601376427702</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.426839480911133</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.49670817134023598</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1.87216486927212</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.27344080102615598</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.607380444084761</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.63192039081600804</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.607380444084761</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.61081637482612094</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.41004189221011</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.42311258425797099</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.49812648270865501</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1.95738545478117</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.18053672372986701</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.58572200982307299</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.635876523170681</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.58572200982307299</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.59678247412673802</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.39615307150741202</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.43227526263564903</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.48038002381845102</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1.8771994777023699</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.40206070374138603</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.59532706368253596</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.63501176854417396</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.59532706368253596</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.60522941714013501</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.41479675790418302</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.44491259479010198</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.49110340506698502</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1.8425369048990801</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.29382510608742701</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.50931029190154598</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.308499881939788</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.50931029190154598</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.370888510062027</v>
+      </c>
+      <c r="F10" s="5">
+        <v>9.6396669905505106E-2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>9.7518678333713693E-2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.10975433559245799</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2.9655678317314198</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3.06265039038475</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.515246576807873</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.38643887894798001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.515246576807873</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.414290243912256</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.16669309322850501</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.18259633278757201</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.189660733067746</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2.96815299202756</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2.6627448974952799</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.46201221837733197</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.434786085507194</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.46201221837733197</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.42347969488385201</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.17260319172681299</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.205496217694909</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.237889105073331</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2.5422678924188302</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2.00019892659668</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.401892290375993</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.41732647658959499</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.401892290375993</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.38692220382807102</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.13564906395926199</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.17488359183798799</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.21790040482826301</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2.6675686193675499</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2.34339443858254</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="top10" dxfId="1" priority="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FADA8-07B8-4272-9C6D-6AA1D1013DC4}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="24">
+        <v>1.7767999999999999</v>
+      </c>
+      <c r="C2" s="24">
+        <v>0.64639999999999997</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0.64670000000000005</v>
+      </c>
+      <c r="E2" s="24">
+        <v>0.64639999999999997</v>
+      </c>
+      <c r="F2" s="24">
+        <v>0.63529999999999998</v>
+      </c>
+      <c r="G2" s="24">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="H2" s="24">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="I2" s="24">
+        <v>0.53</v>
+      </c>
+      <c r="J2" s="24">
+        <v>0.20780000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="24">
+        <v>1.6947000000000001</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="D3" s="24">
+        <v>0.65190000000000003</v>
+      </c>
+      <c r="E3" s="24">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F3" s="24">
+        <v>0.63539999999999996</v>
+      </c>
+      <c r="G3" s="24">
+        <v>0.42309999999999998</v>
+      </c>
+      <c r="H3" s="24">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0.53390000000000004</v>
+      </c>
+      <c r="J3" s="24">
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="K3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="24">
+        <v>1.6883999999999999</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.61819999999999997</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0.63349999999999995</v>
+      </c>
+      <c r="E4" s="24">
+        <v>0.61819999999999997</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0.61539999999999995</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0.40839999999999999</v>
+      </c>
+      <c r="H4" s="24">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0.50290000000000001</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0.37409999999999999</v>
+      </c>
+      <c r="K4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1.6657</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0.63390000000000002</v>
+      </c>
+      <c r="D5" s="24">
+        <v>0.64219999999999999</v>
+      </c>
+      <c r="E5" s="24">
+        <v>0.63390000000000002</v>
+      </c>
+      <c r="F5" s="24">
+        <v>0.62919999999999998</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="H5" s="24">
+        <v>0.42380000000000001</v>
+      </c>
+      <c r="I5" s="24">
+        <v>0.52129999999999999</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0.30709999999999998</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1.7873000000000001</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0.62949999999999995</v>
+      </c>
+      <c r="D6" s="24">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="E6" s="24">
+        <v>0.62949999999999995</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0.62539999999999996</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0.4173</v>
+      </c>
+      <c r="H6" s="24">
+        <v>0.4279</v>
+      </c>
+      <c r="I6" s="24">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0.26019999999999999</v>
+      </c>
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1.7862</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0.60429999999999995</v>
+      </c>
+      <c r="D7" s="24">
+        <v>0.63390000000000002</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0.60429999999999995</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0.40670000000000001</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0.42759999999999998</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0.49430000000000002</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0.31490000000000001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1.9443999999999999</v>
+      </c>
+      <c r="C8" s="24">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="D8" s="24">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="E8" s="24">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="F8" s="24">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.32</v>
+      </c>
+      <c r="H8" s="24">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0.38779999999999998</v>
+      </c>
+      <c r="J8" s="24">
+        <v>1.1711</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1.9424999999999999</v>
+      </c>
+      <c r="C9" s="24">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="D9" s="24">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="E9" s="24">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="F9" s="24">
+        <v>0.54520000000000002</v>
+      </c>
+      <c r="G9" s="24">
+        <v>0.30969999999999998</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="I9" s="24">
+        <v>0.40939999999999999</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0.97330000000000005</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="24">
+        <v>2.0699000000000001</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.59109999999999996</v>
+      </c>
+      <c r="D10" s="24">
+        <v>0.55359999999999998</v>
+      </c>
+      <c r="E10" s="24">
+        <v>0.59109999999999996</v>
+      </c>
+      <c r="F10" s="24">
+        <v>0.55049999999999999</v>
+      </c>
+      <c r="G10" s="24">
+        <v>0.30859999999999999</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.3201</v>
+      </c>
+      <c r="I10" s="24">
+        <v>0.41320000000000001</v>
+      </c>
+      <c r="J10" s="24">
+        <v>1.0298</v>
+      </c>
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="24">
+        <v>1.6728000000000001</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.62139999999999995</v>
+      </c>
+      <c r="D11" s="24">
+        <v>0.63560000000000005</v>
+      </c>
+      <c r="E11" s="24">
+        <v>0.62139999999999995</v>
+      </c>
+      <c r="F11" s="24">
+        <v>0.61719999999999997</v>
+      </c>
+      <c r="G11" s="24">
+        <v>0.40949999999999998</v>
+      </c>
+      <c r="H11" s="24">
+        <v>0.41689999999999999</v>
+      </c>
+      <c r="I11" s="24">
+        <v>0.50239999999999996</v>
+      </c>
+      <c r="J11" s="24">
+        <v>0.45639999999999997</v>
+      </c>
+      <c r="K11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="24">
+        <v>2.3994</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0.4536</v>
+      </c>
+      <c r="D12" s="24">
+        <v>0.40179999999999999</v>
+      </c>
+      <c r="E12" s="24">
+        <v>0.4536</v>
+      </c>
+      <c r="F12" s="24">
+        <v>0.40570000000000001</v>
+      </c>
+      <c r="G12" s="24">
+        <v>7.3800000000000004E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.1179</v>
+      </c>
+      <c r="I12" s="24">
+        <v>0.24260000000000001</v>
+      </c>
+      <c r="J12" s="24">
+        <v>2.8473000000000002</v>
+      </c>
+      <c r="K12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="24">
+        <v>2.2511999999999999</v>
+      </c>
+      <c r="C13" s="24">
+        <v>0.49990000000000001</v>
+      </c>
+      <c r="D13" s="24">
+        <v>0.48170000000000002</v>
+      </c>
+      <c r="E13" s="24">
+        <v>0.49990000000000001</v>
+      </c>
+      <c r="F13" s="24">
+        <v>0.4667</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0.19670000000000001</v>
+      </c>
+      <c r="H13" s="24">
+        <v>0.22209999999999999</v>
+      </c>
+      <c r="I13" s="24">
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="J13" s="24">
+        <v>1.6642999999999999</v>
+      </c>
+      <c r="K13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="21">
+        <f>AVERAGE(B2:B13)</f>
+        <v>1.8899416666666669</v>
+      </c>
+      <c r="C14" s="21">
+        <f t="shared" ref="C14:J14" si="0">AVERAGE(C2:C13)</f>
+        <v>0.59171666666666667</v>
+      </c>
+      <c r="D14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.58432499999999998</v>
+      </c>
+      <c r="E14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.59171666666666667</v>
+      </c>
+      <c r="F14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.57333333333333336</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.34311666666666657</v>
+      </c>
+      <c r="H14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.35570833333333335</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.44522500000000004</v>
+      </c>
+      <c r="J14" s="21">
+        <f t="shared" si="0"/>
+        <v>0.81899166666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="top10" dxfId="14" priority="2" rank="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="top10" dxfId="13" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8396,506 +10523,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14754CE1-3768-4101-A92B-9F9CAC51DA21}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42E03F8-CCBA-4CA7-B914-11C40186E5A7}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="37" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.62980316645271694</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.64070682392547296</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0.62980316645271694</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.62361311380078999</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.41593739817863301</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0.42634337722848198</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0.51826169256072097</v>
-      </c>
-      <c r="I2" s="5">
-        <v>1.87389085736216</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0.37151831865785201</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.61729316663875999</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.63984646711940696</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0.61729316663875999</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.61527601990859404</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.414389135851153</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.42287389218862298</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.50614562928897899</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2.0001337023406398</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0.36739248523474299</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.63438273241428</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.642481177423322</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0.63438273241428</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0.62911935005546904</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.42442816376158299</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.42890060850480499</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0.52417931412833696</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1.94727685364281</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0.11359201579591099</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.62034694703354298</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.63620151880502396</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0.62034694703354298</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.61658372444569798</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.41837086744815599</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.43265132331836798</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.50547826196024603</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1.75102962477178</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0.47292269510521401</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.60174089784376095</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.63435417780303904</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0.60174089784376095</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.606763867251224</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.40444601376427702</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.426839480911133</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.49670817134023598</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1.87216486927212</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.27344080102615598</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.607380444084761</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.63192039081600804</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0.607380444084761</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.61081637482612094</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.41004189221011</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.42311258425797099</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.49812648270865501</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1.95738545478117</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.18053672372986701</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.58572200982307299</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.635876523170681</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.58572200982307299</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.59678247412673802</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0.39615307150741202</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.43227526263564903</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.48038002381845102</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1.8771994777023699</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0.40206070374138603</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.59532706368253596</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.63501176854417396</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.59532706368253596</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.60522941714013501</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.41479675790418302</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.44491259479010198</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.49110340506698502</v>
-      </c>
-      <c r="I9" s="5">
-        <v>1.8425369048990801</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.29382510608742701</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="5">
-        <v>0.50931029190154598</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0.308499881939788</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.50931029190154598</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.370888510062027</v>
-      </c>
-      <c r="F10" s="5">
-        <v>9.6396669905505106E-2</v>
-      </c>
-      <c r="G10" s="5">
-        <v>9.7518678333713693E-2</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0.10975433559245799</v>
-      </c>
-      <c r="I10" s="5">
-        <v>2.9655678317314198</v>
-      </c>
-      <c r="J10" s="5">
-        <v>3.06265039038475</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.515246576807873</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.38643887894798001</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.515246576807873</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.414290243912256</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.16669309322850501</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.18259633278757201</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0.189660733067746</v>
-      </c>
-      <c r="I11" s="5">
-        <v>2.96815299202756</v>
-      </c>
-      <c r="J11" s="5">
-        <v>2.6627448974952799</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.46201221837733197</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.434786085507194</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.46201221837733197</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0.42347969488385201</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.17260319172681299</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.205496217694909</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0.237889105073331</v>
-      </c>
-      <c r="I12" s="5">
-        <v>2.5422678924188302</v>
-      </c>
-      <c r="J12" s="5">
-        <v>2.00019892659668</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.401892290375993</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.41732647658959499</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.401892290375993</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.38692220382807102</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.13564906395926199</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.17488359183798799</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.21790040482826301</v>
-      </c>
-      <c r="I13" s="5">
-        <v>2.6675686193675499</v>
-      </c>
-      <c r="J13" s="5">
-        <v>2.34339443858254</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FADA8-07B8-4272-9C6D-6AA1D1013DC4}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>17</v>
@@ -8931,534 +10579,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="24">
-        <v>1.7767999999999999</v>
-      </c>
-      <c r="C2" s="24">
-        <v>0.64639999999999997</v>
-      </c>
-      <c r="D2" s="24">
-        <v>0.64670000000000005</v>
-      </c>
-      <c r="E2" s="24">
-        <v>0.64639999999999997</v>
-      </c>
-      <c r="F2" s="24">
-        <v>0.63529999999999998</v>
-      </c>
-      <c r="G2" s="24">
-        <v>0.41860000000000003</v>
-      </c>
-      <c r="H2" s="24">
-        <v>0.40820000000000001</v>
-      </c>
-      <c r="I2" s="24">
-        <v>0.53</v>
-      </c>
-      <c r="J2" s="24">
-        <v>0.20780000000000001</v>
-      </c>
-      <c r="K2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="24">
-        <v>1.6947000000000001</v>
-      </c>
-      <c r="C3" s="24">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="D3" s="24">
-        <v>0.65190000000000003</v>
-      </c>
-      <c r="E3" s="24">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F3" s="24">
-        <v>0.63539999999999996</v>
-      </c>
-      <c r="G3" s="24">
-        <v>0.42309999999999998</v>
-      </c>
-      <c r="H3" s="24">
-        <v>0.42299999999999999</v>
-      </c>
-      <c r="I3" s="24">
-        <v>0.53390000000000004</v>
-      </c>
-      <c r="J3" s="24">
-        <v>0.22159999999999999</v>
-      </c>
-      <c r="K3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="24">
-        <v>1.6883999999999999</v>
-      </c>
-      <c r="C4" s="24">
-        <v>0.61819999999999997</v>
-      </c>
-      <c r="D4" s="24">
-        <v>0.63349999999999995</v>
-      </c>
-      <c r="E4" s="24">
-        <v>0.61819999999999997</v>
-      </c>
-      <c r="F4" s="24">
-        <v>0.61539999999999995</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0.40839999999999999</v>
-      </c>
-      <c r="H4" s="24">
-        <v>0.41860000000000003</v>
-      </c>
-      <c r="I4" s="24">
-        <v>0.50290000000000001</v>
-      </c>
-      <c r="J4" s="24">
-        <v>0.37409999999999999</v>
-      </c>
-      <c r="K4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="24">
-        <v>1.6657</v>
-      </c>
-      <c r="C5" s="24">
-        <v>0.63390000000000002</v>
-      </c>
-      <c r="D5" s="24">
-        <v>0.64219999999999999</v>
-      </c>
-      <c r="E5" s="24">
-        <v>0.63390000000000002</v>
-      </c>
-      <c r="F5" s="24">
-        <v>0.62919999999999998</v>
-      </c>
-      <c r="G5" s="24">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="H5" s="24">
-        <v>0.42380000000000001</v>
-      </c>
-      <c r="I5" s="24">
-        <v>0.52129999999999999</v>
-      </c>
-      <c r="J5" s="24">
-        <v>0.30709999999999998</v>
-      </c>
-      <c r="K5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="24">
-        <v>1.7873000000000001</v>
-      </c>
-      <c r="C6" s="24">
-        <v>0.62949999999999995</v>
-      </c>
-      <c r="D6" s="24">
-        <v>0.64200000000000002</v>
-      </c>
-      <c r="E6" s="24">
-        <v>0.62949999999999995</v>
-      </c>
-      <c r="F6" s="24">
-        <v>0.62539999999999996</v>
-      </c>
-      <c r="G6" s="24">
-        <v>0.4173</v>
-      </c>
-      <c r="H6" s="24">
-        <v>0.4279</v>
-      </c>
-      <c r="I6" s="24">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="J6" s="24">
-        <v>0.26019999999999999</v>
-      </c>
-      <c r="K6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="24">
-        <v>1.7862</v>
-      </c>
-      <c r="C7" s="24">
-        <v>0.60429999999999995</v>
-      </c>
-      <c r="D7" s="24">
-        <v>0.63390000000000002</v>
-      </c>
-      <c r="E7" s="24">
-        <v>0.60429999999999995</v>
-      </c>
-      <c r="F7" s="24">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="G7" s="24">
-        <v>0.40670000000000001</v>
-      </c>
-      <c r="H7" s="24">
-        <v>0.42759999999999998</v>
-      </c>
-      <c r="I7" s="24">
-        <v>0.49430000000000002</v>
-      </c>
-      <c r="J7" s="24">
-        <v>0.31490000000000001</v>
-      </c>
-      <c r="K7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="24">
-        <v>1.9443999999999999</v>
-      </c>
-      <c r="C8" s="24">
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="D8" s="24">
-        <v>0.54700000000000004</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.32</v>
-      </c>
-      <c r="H8" s="24">
-        <v>0.33119999999999999</v>
-      </c>
-      <c r="I8" s="24">
-        <v>0.38779999999999998</v>
-      </c>
-      <c r="J8" s="24">
-        <v>1.1711</v>
-      </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="24">
-        <v>1.9424999999999999</v>
-      </c>
-      <c r="C9" s="24">
-        <v>0.57899999999999996</v>
-      </c>
-      <c r="D9" s="24">
-        <v>0.54200000000000004</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0.57899999999999996</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.54520000000000002</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.30969999999999998</v>
-      </c>
-      <c r="H9" s="24">
-        <v>0.33119999999999999</v>
-      </c>
-      <c r="I9" s="24">
-        <v>0.40939999999999999</v>
-      </c>
-      <c r="J9" s="24">
-        <v>0.97330000000000005</v>
-      </c>
-      <c r="K9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="24">
-        <v>2.0699000000000001</v>
-      </c>
-      <c r="C10" s="24">
-        <v>0.59109999999999996</v>
-      </c>
-      <c r="D10" s="24">
-        <v>0.55359999999999998</v>
-      </c>
-      <c r="E10" s="24">
-        <v>0.59109999999999996</v>
-      </c>
-      <c r="F10" s="24">
-        <v>0.55049999999999999</v>
-      </c>
-      <c r="G10" s="24">
-        <v>0.30859999999999999</v>
-      </c>
-      <c r="H10" s="24">
-        <v>0.3201</v>
-      </c>
-      <c r="I10" s="24">
-        <v>0.41320000000000001</v>
-      </c>
-      <c r="J10" s="24">
-        <v>1.0298</v>
-      </c>
-      <c r="K10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="24">
-        <v>1.6728000000000001</v>
-      </c>
-      <c r="C11" s="24">
-        <v>0.62139999999999995</v>
-      </c>
-      <c r="D11" s="24">
-        <v>0.63560000000000005</v>
-      </c>
-      <c r="E11" s="24">
-        <v>0.62139999999999995</v>
-      </c>
-      <c r="F11" s="24">
-        <v>0.61719999999999997</v>
-      </c>
-      <c r="G11" s="24">
-        <v>0.40949999999999998</v>
-      </c>
-      <c r="H11" s="24">
-        <v>0.41689999999999999</v>
-      </c>
-      <c r="I11" s="24">
-        <v>0.50239999999999996</v>
-      </c>
-      <c r="J11" s="24">
-        <v>0.45639999999999997</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24">
-        <v>2.3994</v>
-      </c>
-      <c r="C12" s="24">
-        <v>0.4536</v>
-      </c>
-      <c r="D12" s="24">
-        <v>0.40179999999999999</v>
-      </c>
-      <c r="E12" s="24">
-        <v>0.4536</v>
-      </c>
-      <c r="F12" s="24">
-        <v>0.40570000000000001</v>
-      </c>
-      <c r="G12" s="24">
-        <v>7.3800000000000004E-2</v>
-      </c>
-      <c r="H12" s="24">
-        <v>0.1179</v>
-      </c>
-      <c r="I12" s="24">
-        <v>0.24260000000000001</v>
-      </c>
-      <c r="J12" s="24">
-        <v>2.8473000000000002</v>
-      </c>
-      <c r="K12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="24">
-        <v>2.2511999999999999</v>
-      </c>
-      <c r="C13" s="24">
-        <v>0.49990000000000001</v>
-      </c>
-      <c r="D13" s="24">
-        <v>0.48170000000000002</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0.49990000000000001</v>
-      </c>
-      <c r="F13" s="24">
-        <v>0.4667</v>
-      </c>
-      <c r="G13" s="24">
-        <v>0.19670000000000001</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.22209999999999999</v>
-      </c>
-      <c r="I13" s="24">
-        <v>0.28989999999999999</v>
-      </c>
-      <c r="J13" s="24">
-        <v>1.6642999999999999</v>
-      </c>
-      <c r="K13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="21">
-        <f>AVERAGE(B2:B13)</f>
-        <v>1.8899416666666669</v>
-      </c>
-      <c r="C14" s="21">
-        <f t="shared" ref="C14:J14" si="0">AVERAGE(C2:C13)</f>
-        <v>0.59171666666666667</v>
-      </c>
-      <c r="D14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.58432499999999998</v>
-      </c>
-      <c r="E14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.59171666666666667</v>
-      </c>
-      <c r="F14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.57333333333333336</v>
-      </c>
-      <c r="G14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.34311666666666657</v>
-      </c>
-      <c r="H14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.35570833333333335</v>
-      </c>
-      <c r="I14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.44522500000000004</v>
-      </c>
-      <c r="J14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.81899166666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C13">
-    <cfRule type="top10" dxfId="12" priority="2" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="11" priority="1" rank="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42E03F8-CCBA-4CA7-B914-11C40186E5A7}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -9496,7 +10617,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -9534,7 +10655,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -9572,7 +10693,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -9610,7 +10731,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -9648,7 +10769,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -9686,7 +10807,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -9724,7 +10845,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -9762,7 +10883,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -9800,7 +10921,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -9838,7 +10959,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -9876,7 +10997,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
@@ -9914,7 +11035,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="17">
         <f>AVERAGE(B2:B13)</f>
         <v>2.0257684019102653</v>
@@ -9959,531 +11080,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="10" priority="1" rank="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDAE853-41FD-426B-83A6-86030E6D9E5C}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="41.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="18">
-        <v>1.7633318481648801</v>
-      </c>
-      <c r="C2" s="18">
-        <v>0.63773534445870705</v>
-      </c>
-      <c r="D2" s="18">
-        <v>0.64585828517214805</v>
-      </c>
-      <c r="E2" s="18">
-        <v>0.63773534445870705</v>
-      </c>
-      <c r="F2" s="18">
-        <v>0.63209686587194303</v>
-      </c>
-      <c r="G2" s="18">
-        <v>0.42266767856564602</v>
-      </c>
-      <c r="H2" s="18">
-        <v>0.424866302265412</v>
-      </c>
-      <c r="I2" s="18">
-        <v>0.52335837026211496</v>
-      </c>
-      <c r="J2" s="18">
-        <v>0.15858271169754501</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="18">
-        <v>1.6060506546642701</v>
-      </c>
-      <c r="C3" s="18">
-        <v>0.64292141076445097</v>
-      </c>
-      <c r="D3" s="18">
-        <v>0.64788097263192801</v>
-      </c>
-      <c r="E3" s="18">
-        <v>0.64292141076445097</v>
-      </c>
-      <c r="F3" s="18">
-        <v>0.62880265308775896</v>
-      </c>
-      <c r="G3" s="18">
-        <v>0.419193447998292</v>
-      </c>
-      <c r="H3" s="18">
-        <v>0.41426456144062401</v>
-      </c>
-      <c r="I3" s="18">
-        <v>0.522161283524194</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0.41292034835052499</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="18">
-        <v>1.7065480208978401</v>
-      </c>
-      <c r="C4" s="18">
-        <v>0.64231072445163795</v>
-      </c>
-      <c r="D4" s="18">
-        <v>0.64914280521756695</v>
-      </c>
-      <c r="E4" s="18">
-        <v>0.64231072445163795</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0.63456516154213005</v>
-      </c>
-      <c r="G4" s="18">
-        <v>0.41642881057056802</v>
-      </c>
-      <c r="H4" s="18">
-        <v>0.42394526186094</v>
-      </c>
-      <c r="I4" s="18">
-        <v>0.52965118805703404</v>
-      </c>
-      <c r="J4" s="18">
-        <v>0.280976879672932</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="18">
-        <v>1.6844555593527299</v>
-      </c>
-      <c r="C5" s="18">
-        <v>0.64170271250767397</v>
-      </c>
-      <c r="D5" s="18">
-        <v>0.65118305208096705</v>
-      </c>
-      <c r="E5" s="18">
-        <v>0.64170271250767397</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0.63679617815674805</v>
-      </c>
-      <c r="G5" s="18">
-        <v>0.41874004653369301</v>
-      </c>
-      <c r="H5" s="18">
-        <v>0.42851655284519002</v>
-      </c>
-      <c r="I5" s="18">
-        <v>0.52903004661683195</v>
-      </c>
-      <c r="J5" s="18">
-        <v>0.261424004426486</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="18">
-        <v>2.02518721718977</v>
-      </c>
-      <c r="C6" s="18">
-        <v>0.60158369146620505</v>
-      </c>
-      <c r="D6" s="18">
-        <v>0.56010813354540401</v>
-      </c>
-      <c r="E6" s="18">
-        <v>0.60158369146620505</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0.56306214712604796</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0.33591177116505999</v>
-      </c>
-      <c r="H6" s="18">
-        <v>0.33577325471428998</v>
-      </c>
-      <c r="I6" s="18">
-        <v>0.41325757668533702</v>
-      </c>
-      <c r="J6" s="18">
-        <v>0.91616751128435603</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="18">
-        <v>1.7286468746821999</v>
-      </c>
-      <c r="C7" s="18">
-        <v>0.62583742628044103</v>
-      </c>
-      <c r="D7" s="18">
-        <v>0.64314354051438005</v>
-      </c>
-      <c r="E7" s="18">
-        <v>0.62583742628044103</v>
-      </c>
-      <c r="F7" s="18">
-        <v>0.62471608290857195</v>
-      </c>
-      <c r="G7" s="18">
-        <v>0.40170177814221403</v>
-      </c>
-      <c r="H7" s="18">
-        <v>0.41503025460943599</v>
-      </c>
-      <c r="I7" s="18">
-        <v>0.51124042310741102</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0.33378010952758003</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="18">
-        <v>1.66500821949505</v>
-      </c>
-      <c r="C8" s="18">
-        <v>0.59991162955107802</v>
-      </c>
-      <c r="D8" s="18">
-        <v>0.62326123009955003</v>
-      </c>
-      <c r="E8" s="18">
-        <v>0.59991162955107802</v>
-      </c>
-      <c r="F8" s="18">
-        <v>0.59561874325319897</v>
-      </c>
-      <c r="G8" s="18">
-        <v>0.37842957103013303</v>
-      </c>
-      <c r="H8" s="18">
-        <v>0.39554160615859202</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0.47365818700672502</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0.701845622032506</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="18">
-        <v>1.6963374429723099</v>
-      </c>
-      <c r="C9" s="18">
-        <v>0.60921250302319896</v>
-      </c>
-      <c r="D9" s="18">
-        <v>0.63388463041651699</v>
-      </c>
-      <c r="E9" s="18">
-        <v>0.60921250302319896</v>
-      </c>
-      <c r="F9" s="18">
-        <v>0.609708652447846</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0.39908908887107902</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0.41791952793020198</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0.490704431636454</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0.50646139980168903</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="18">
-        <v>2.30053117048086</v>
-      </c>
-      <c r="C10" s="18">
-        <v>0.59608949135830003</v>
-      </c>
-      <c r="D10" s="18">
-        <v>0.55361795674316705</v>
-      </c>
-      <c r="E10" s="18">
-        <v>0.59608949135830003</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0.55691609611373105</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0.33008068820880498</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0.33489385401965799</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0.40843403254931898</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0.82586389531957105</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="18">
-        <v>2.09086211956128</v>
-      </c>
-      <c r="C11" s="18">
-        <v>0.59258804487358296</v>
-      </c>
-      <c r="D11" s="18">
-        <v>0.56358777540334104</v>
-      </c>
-      <c r="E11" s="18">
-        <v>0.59258804487358296</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0.55670726127855996</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0.32178395353003297</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0.33476428167644501</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0.42888508012367699</v>
-      </c>
-      <c r="J11" s="18">
-        <v>1.03129530288474</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="18">
-        <v>2.7874045825586</v>
-      </c>
-      <c r="C12" s="18">
-        <v>0.45393260125392998</v>
-      </c>
-      <c r="D12" s="18">
-        <v>0.28674363044323398</v>
-      </c>
-      <c r="E12" s="18">
-        <v>0.45393260125392998</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0.34138126396280599</v>
-      </c>
-      <c r="G12" s="18">
-        <v>2.6233249079102398E-2</v>
-      </c>
-      <c r="H12" s="18">
-        <v>4.7457167005305903E-2</v>
-      </c>
-      <c r="I12" s="18">
-        <v>0.13642573046380399</v>
-      </c>
-      <c r="J12" s="18">
-        <v>3.4645091849998302</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="18">
-        <v>2.3795432114019599</v>
-      </c>
-      <c r="C13" s="18">
-        <v>0.51372544231735195</v>
-      </c>
-      <c r="D13" s="18">
-        <v>0.48977421624057998</v>
-      </c>
-      <c r="E13" s="18">
-        <v>0.51372544231735195</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0.48758786597237003</v>
-      </c>
-      <c r="G13" s="18">
-        <v>0.214164303979616</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0.233778361020088</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0.33398580589150201</v>
-      </c>
-      <c r="J13" s="18">
-        <v>1.42454044189455</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="17">
-        <f>AVERAGE(B2:B13)</f>
-        <v>1.9528255767851457</v>
-      </c>
-      <c r="C14" s="17">
-        <f t="shared" ref="C14:J14" si="0">AVERAGE(C2:C13)</f>
-        <v>0.59646258519221307</v>
-      </c>
-      <c r="D14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.57901551904239867</v>
-      </c>
-      <c r="E14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.59646258519221307</v>
-      </c>
-      <c r="F14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.5723299143101428</v>
-      </c>
-      <c r="G14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.34036869897285343</v>
-      </c>
-      <c r="H14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.35056258212884855</v>
-      </c>
-      <c r="I14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.44173267966036706</v>
-      </c>
-      <c r="J14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.85986395099102575</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="9" priority="1" rank="3"/>
+    <cfRule type="top10" dxfId="12" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10491,21 +11088,27 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41F17F3-0237-45E9-80B4-1366CB6A8587}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDAE853-41FD-426B-83A6-86030E6D9E5C}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="41.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
@@ -10540,508 +11143,468 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="B2" s="18">
-        <v>2.2289966613599401</v>
+        <v>1.7633318481648801</v>
       </c>
       <c r="C2" s="18">
-        <v>0.639415313203475</v>
+        <v>0.63773534445870705</v>
       </c>
       <c r="D2" s="18">
-        <v>0.65068682015205304</v>
+        <v>0.64585828517214805</v>
       </c>
       <c r="E2" s="18">
-        <v>0.639415313203475</v>
+        <v>0.63773534445870705</v>
       </c>
       <c r="F2" s="18">
-        <v>0.63246585366907804</v>
+        <v>0.63209686587194303</v>
       </c>
       <c r="G2" s="18">
-        <v>0.42430011001183299</v>
+        <v>0.42266767856564602</v>
       </c>
       <c r="H2" s="18">
-        <v>0.41268145071012302</v>
+        <v>0.424866302265412</v>
       </c>
       <c r="I2" s="18">
-        <v>0.52519166776561099</v>
+        <v>0.52335837026211496</v>
       </c>
       <c r="J2" s="18">
-        <v>0.115670414946195</v>
-      </c>
-      <c r="K2" s="4">
-        <v>11206</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.15858271169754501</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>259</v>
+        <v>102</v>
       </c>
       <c r="B3" s="18">
-        <v>2.2038158333701299</v>
+        <v>1.6060506546642701</v>
       </c>
       <c r="C3" s="18">
-        <v>0.63605770125206895</v>
+        <v>0.64292141076445097</v>
       </c>
       <c r="D3" s="18">
-        <v>0.64510310003867499</v>
+        <v>0.64788097263192801</v>
       </c>
       <c r="E3" s="18">
-        <v>0.63605770125206895</v>
+        <v>0.64292141076445097</v>
       </c>
       <c r="F3" s="18">
-        <v>0.62624056297897601</v>
+        <v>0.62880265308775896</v>
       </c>
       <c r="G3" s="18">
-        <v>0.41274061304149701</v>
+        <v>0.419193447998292</v>
       </c>
       <c r="H3" s="18">
-        <v>0.41722744778813498</v>
+        <v>0.41426456144062401</v>
       </c>
       <c r="I3" s="18">
-        <v>0.52165768424714698</v>
+        <v>0.522161283524194</v>
       </c>
       <c r="J3" s="18">
-        <v>0.37937119210269898</v>
-      </c>
-      <c r="K3" s="4">
-        <v>15239</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.41292034835052499</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>261</v>
+        <v>104</v>
       </c>
       <c r="B4" s="18">
-        <v>1.8410535421858401</v>
+        <v>1.7065480208978401</v>
       </c>
       <c r="C4" s="18">
-        <v>0.63468505237111805</v>
+        <v>0.64231072445163795</v>
       </c>
       <c r="D4" s="18">
-        <v>0.64252379832189399</v>
+        <v>0.64914280521756695</v>
       </c>
       <c r="E4" s="18">
-        <v>0.63468505237111805</v>
+        <v>0.64231072445163795</v>
       </c>
       <c r="F4" s="18">
-        <v>0.62799656466898301</v>
+        <v>0.63456516154213005</v>
       </c>
       <c r="G4" s="18">
-        <v>0.40988431119723201</v>
+        <v>0.41642881057056802</v>
       </c>
       <c r="H4" s="18">
-        <v>0.43197689167018299</v>
+        <v>0.42394526186094</v>
       </c>
       <c r="I4" s="18">
-        <v>0.52129152263788903</v>
+        <v>0.52965118805703404</v>
       </c>
       <c r="J4" s="18">
-        <v>0.58198165563455395</v>
-      </c>
-      <c r="K4" s="4">
-        <v>10105</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.280976879672932</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>263</v>
+        <v>106</v>
       </c>
       <c r="B5" s="18">
-        <v>2.2058255382427299</v>
+        <v>1.6844555593527299</v>
       </c>
       <c r="C5" s="18">
-        <v>0.64993837323956705</v>
+        <v>0.64170271250767397</v>
       </c>
       <c r="D5" s="18">
-        <v>0.64886394640481104</v>
+        <v>0.65118305208096705</v>
       </c>
       <c r="E5" s="18">
-        <v>0.64993837323956705</v>
+        <v>0.64170271250767397</v>
       </c>
       <c r="F5" s="18">
-        <v>0.63979939601325797</v>
+        <v>0.63679617815674805</v>
       </c>
       <c r="G5" s="18">
-        <v>0.426306397695707</v>
+        <v>0.41874004653369301</v>
       </c>
       <c r="H5" s="18">
-        <v>0.42492185735184002</v>
+        <v>0.42851655284519002</v>
       </c>
       <c r="I5" s="18">
-        <v>0.53617965426203995</v>
+        <v>0.52903004661683195</v>
       </c>
       <c r="J5" s="18">
-        <v>0.33220212649571501</v>
-      </c>
-      <c r="K5" s="4">
-        <v>16547</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.261424004426486</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>265</v>
+        <v>108</v>
       </c>
       <c r="B6" s="18">
-        <v>2.0051634905178299</v>
+        <v>2.02518721718977</v>
       </c>
       <c r="C6" s="18">
-        <v>0.62522767018287995</v>
+        <v>0.60158369146620505</v>
       </c>
       <c r="D6" s="18">
-        <v>0.63519005768422998</v>
+        <v>0.56010813354540401</v>
       </c>
       <c r="E6" s="18">
-        <v>0.62522767018287995</v>
+        <v>0.60158369146620505</v>
       </c>
       <c r="F6" s="18">
-        <v>0.61969057546065898</v>
+        <v>0.56306214712604796</v>
       </c>
       <c r="G6" s="18">
-        <v>0.407377079440775</v>
+        <v>0.33591177116505999</v>
       </c>
       <c r="H6" s="18">
-        <v>0.42234023395870701</v>
+        <v>0.33577325471428998</v>
       </c>
       <c r="I6" s="18">
-        <v>0.50917153772274504</v>
+        <v>0.41325757668533702</v>
       </c>
       <c r="J6" s="18">
-        <v>0.38880028879171102</v>
-      </c>
-      <c r="K6" s="4">
-        <v>21604</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.91616751128435603</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="B7" s="18">
-        <v>2.1132766196095298</v>
+        <v>1.7286468746821999</v>
       </c>
       <c r="C7" s="18">
-        <v>0.63392669438708105</v>
+        <v>0.62583742628044103</v>
       </c>
       <c r="D7" s="18">
-        <v>0.63868013050838801</v>
+        <v>0.64314354051438005</v>
       </c>
       <c r="E7" s="18">
-        <v>0.63392669438708105</v>
+        <v>0.62583742628044103</v>
       </c>
       <c r="F7" s="18">
-        <v>0.62587792038177803</v>
+        <v>0.62471608290857195</v>
       </c>
       <c r="G7" s="18">
-        <v>0.41639088686973402</v>
+        <v>0.40170177814221403</v>
       </c>
       <c r="H7" s="18">
-        <v>0.422453815988311</v>
+        <v>0.41503025460943599</v>
       </c>
       <c r="I7" s="18">
-        <v>0.51997285168371099</v>
+        <v>0.51124042310741102</v>
       </c>
       <c r="J7" s="18">
-        <v>0.30389512791704798</v>
-      </c>
-      <c r="K7" s="4">
-        <v>22627</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.33378010952758003</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="B8" s="18">
-        <v>2.24683170376754</v>
+        <v>1.66500821949505</v>
       </c>
       <c r="C8" s="18">
-        <v>0.59014460196089302</v>
+        <v>0.59991162955107802</v>
       </c>
       <c r="D8" s="18">
-        <v>0.54263316194877398</v>
+        <v>0.62326123009955003</v>
       </c>
       <c r="E8" s="18">
-        <v>0.59014460196089302</v>
+        <v>0.59991162955107802</v>
       </c>
       <c r="F8" s="18">
-        <v>0.54833042705742696</v>
+        <v>0.59561874325319897</v>
       </c>
       <c r="G8" s="18">
-        <v>0.31597091421435203</v>
+        <v>0.37842957103013303</v>
       </c>
       <c r="H8" s="18">
-        <v>0.32295853702567701</v>
+        <v>0.39554160615859202</v>
       </c>
       <c r="I8" s="18">
-        <v>0.398659970981113</v>
+        <v>0.47365818700672502</v>
       </c>
       <c r="J8" s="18">
-        <v>1.1682616644029</v>
-      </c>
-      <c r="K8" s="4">
-        <v>23221</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.701845622032506</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>271</v>
+        <v>114</v>
       </c>
       <c r="B9" s="18">
-        <v>2.4295915400109598</v>
+        <v>1.6963374429723099</v>
       </c>
       <c r="C9" s="18">
-        <v>0.56665631802199001</v>
+        <v>0.60921250302319896</v>
       </c>
       <c r="D9" s="18">
-        <v>0.46465848740497701</v>
+        <v>0.63388463041651699</v>
       </c>
       <c r="E9" s="18">
-        <v>0.56665631802199001</v>
+        <v>0.60921250302319896</v>
       </c>
       <c r="F9" s="18">
-        <v>0.48937571606485297</v>
+        <v>0.609708652447846</v>
       </c>
       <c r="G9" s="18">
-        <v>0.22188853282277399</v>
+        <v>0.39908908887107902</v>
       </c>
       <c r="H9" s="18">
-        <v>0.234643182639731</v>
+        <v>0.41791952793020198</v>
       </c>
       <c r="I9" s="18">
-        <v>0.33549019201014901</v>
+        <v>0.490704431636454</v>
       </c>
       <c r="J9" s="18">
-        <v>1.87515853551637</v>
-      </c>
-      <c r="K9" s="4">
-        <v>22242</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.50646139980168903</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>273</v>
+        <v>116</v>
       </c>
       <c r="B10" s="18">
-        <v>2.3158342166644701</v>
+        <v>2.30053117048086</v>
       </c>
       <c r="C10" s="18">
-        <v>0.60478642257818405</v>
+        <v>0.59608949135830003</v>
       </c>
       <c r="D10" s="18">
-        <v>0.55555180994171904</v>
+        <v>0.55361795674316705</v>
       </c>
       <c r="E10" s="18">
-        <v>0.60478642257818405</v>
+        <v>0.59608949135830003</v>
       </c>
       <c r="F10" s="18">
-        <v>0.56273941066389899</v>
+        <v>0.55691609611373105</v>
       </c>
       <c r="G10" s="18">
-        <v>0.32746866097302302</v>
+        <v>0.33008068820880498</v>
       </c>
       <c r="H10" s="18">
-        <v>0.32765408222336001</v>
+        <v>0.33489385401965799</v>
       </c>
       <c r="I10" s="18">
-        <v>0.41949665711399398</v>
+        <v>0.40843403254931898</v>
       </c>
       <c r="J10" s="18">
-        <v>0.98818393929395798</v>
-      </c>
-      <c r="K10" s="4">
-        <v>21300</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.82586389531957105</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>275</v>
+        <v>118</v>
       </c>
       <c r="B11" s="18">
-        <v>2.5296481059818698</v>
+        <v>2.09086211956128</v>
       </c>
       <c r="C11" s="18">
-        <v>0.59090726219047096</v>
+        <v>0.59258804487358296</v>
       </c>
       <c r="D11" s="18">
-        <v>0.55349975826229703</v>
+        <v>0.56358777540334104</v>
       </c>
       <c r="E11" s="18">
-        <v>0.59090726219047096</v>
+        <v>0.59258804487358296</v>
       </c>
       <c r="F11" s="18">
-        <v>0.55485771768875503</v>
+        <v>0.55670726127855996</v>
       </c>
       <c r="G11" s="18">
-        <v>0.31925129866330498</v>
+        <v>0.32178395353003297</v>
       </c>
       <c r="H11" s="18">
-        <v>0.33020663650608501</v>
+        <v>0.33476428167644501</v>
       </c>
       <c r="I11" s="18">
-        <v>0.40628760788485901</v>
+        <v>0.42888508012367699</v>
       </c>
       <c r="J11" s="18">
-        <v>1.0116982194898101</v>
-      </c>
-      <c r="K11" s="4">
-        <v>22891</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1.03129530288474</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="B12" s="18">
-        <v>2.6606197288850399</v>
+        <v>2.7874045825586</v>
       </c>
       <c r="C12" s="18">
-        <v>0.51098072593998201</v>
+        <v>0.45393260125392998</v>
       </c>
       <c r="D12" s="18">
-        <v>0.41254807289860801</v>
+        <v>0.28674363044323398</v>
       </c>
       <c r="E12" s="18">
-        <v>0.51098072593998201</v>
+        <v>0.45393260125392998</v>
       </c>
       <c r="F12" s="18">
-        <v>0.43818459664591197</v>
+        <v>0.34138126396280599</v>
       </c>
       <c r="G12" s="18">
-        <v>0.13111995483833899</v>
+        <v>2.6233249079102398E-2</v>
       </c>
       <c r="H12" s="18">
-        <v>0.141765848596106</v>
+        <v>4.7457167005305903E-2</v>
       </c>
       <c r="I12" s="18">
-        <v>0.26107131127136202</v>
+        <v>0.13642573046380399</v>
       </c>
       <c r="J12" s="18">
-        <v>2.3707823125426999</v>
-      </c>
-      <c r="K12" s="4">
-        <v>12850</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3.4645091849998302</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>279</v>
+        <v>122</v>
       </c>
       <c r="B13" s="18">
-        <v>3.0558207325818998</v>
+        <v>2.3795432114019599</v>
       </c>
       <c r="C13" s="18">
-        <v>0.46613644397313497</v>
+        <v>0.51372544231735195</v>
       </c>
       <c r="D13" s="18">
-        <v>0.27768801298037998</v>
+        <v>0.48977421624057998</v>
       </c>
       <c r="E13" s="18">
-        <v>0.46613644397313497</v>
+        <v>0.51372544231735195</v>
       </c>
       <c r="F13" s="18">
-        <v>0.33978112073896499</v>
+        <v>0.48758786597237003</v>
       </c>
       <c r="G13" s="18">
-        <v>2.5020099038473201E-2</v>
+        <v>0.214164303979616</v>
       </c>
       <c r="H13" s="18">
-        <v>4.1136765674076398E-2</v>
+        <v>0.233778361020088</v>
       </c>
       <c r="I13" s="18">
-        <v>0.14560984657555501</v>
+        <v>0.33398580589150201</v>
       </c>
       <c r="J13" s="18">
-        <v>3.40151405680778</v>
-      </c>
-      <c r="K13" s="4">
-        <v>10847</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1.42454044189455</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="17">
         <f>AVERAGE(B2:B13)</f>
-        <v>2.3197064760981481</v>
+        <v>1.9528255767851457</v>
       </c>
       <c r="C14" s="17">
-        <f t="shared" ref="C14:K14" si="0">AVERAGE(C2:C13)</f>
-        <v>0.59573854827507045</v>
+        <f t="shared" ref="C14:J14" si="0">AVERAGE(C2:C13)</f>
+        <v>0.59646258519221307</v>
       </c>
       <c r="D14" s="17">
         <f t="shared" si="0"/>
-        <v>0.55563559637890048</v>
+        <v>0.57901551904239867</v>
       </c>
       <c r="E14" s="17">
         <f t="shared" si="0"/>
-        <v>0.59573854827507045</v>
+        <v>0.59646258519221307</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
-        <v>0.55877832183604514</v>
+        <v>0.5723299143101428</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="0"/>
-        <v>0.31980990490058703</v>
+        <v>0.34036869897285343</v>
       </c>
       <c r="H14" s="17">
         <f t="shared" si="0"/>
-        <v>0.32749722917769458</v>
+        <v>0.35056258212884855</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="0"/>
-        <v>0.42500670867968132</v>
+        <v>0.44173267966036706</v>
       </c>
       <c r="J14" s="17">
         <f t="shared" si="0"/>
-        <v>1.0764599611617867</v>
-      </c>
-      <c r="K14" s="17">
-        <f t="shared" si="0"/>
-        <v>17556.583333333332</v>
+        <v>0.85986395099102575</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G13">
-    <cfRule type="top10" dxfId="8" priority="1" rank="3"/>
+    <cfRule type="top10" dxfId="11" priority="1" rank="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
